--- a/Games/Codes/Dialogues/NeuralRust_Dialogue.xlsx
+++ b/Games/Codes/Dialogues/NeuralRust_Dialogue.xlsx
@@ -9,33 +9,127 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11865" activeTab="5"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11865" activeTab="6"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="CAST" sheetId="1" r:id="rId4"/>
-    <x:sheet name="BGM" sheetId="2" r:id="rId5"/>
-    <x:sheet name="SFX" sheetId="3" r:id="rId6"/>
-    <x:sheet name="FX" sheetId="4" r:id="rId7"/>
-    <x:sheet name="_양식" sheetId="5" r:id="rId8"/>
-    <x:sheet name="Welcome" sheetId="6" r:id="rId9"/>
+    <x:sheet name="BG" sheetId="2" r:id="rId5"/>
+    <x:sheet name="BGM" sheetId="3" r:id="rId6"/>
+    <x:sheet name="SFX" sheetId="4" r:id="rId7"/>
+    <x:sheet name="FX" sheetId="5" r:id="rId8"/>
+    <x:sheet name="_양식" sheetId="6" r:id="rId9"/>
+    <x:sheet name="Welcome" sheetId="7" r:id="rId10"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="245">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="257">
   <x:si>
     <x:t>// char: CAST 탭 단축어 (P 고정)  |  expr: 001~999, 공백=이전 표정 유지  |  choice: 1=선택지 줄</x:t>
   </x:si>
   <x:si>
+    <x:t>// sfx: SFX 탭 별칭 (복합: Happy|Beep)  |  fx: FX 탭 예약어 (복합: shake_char|fade_out, 파라미터: shake_char:intensity=5)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sprite.x-=dist; tweens: x+=dist, alpha→1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sprite.x+=dist; tweens: x-=dist, alpha→1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 태그는 대사 시트 bg 컬럼에 입력  |  공백=이전 배경 유지  |  NONE=배경 제거  |  전환 접두어: instant:A  fade_black:B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// target — screen: 카메라  |  char: 현재 발화 캐릭터  |  ui: 대화창  |  all: 전체</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.shake(dur, intensity)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.fadeIn(dur, r, g, b)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogManager.setTypingSpeed(speed)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: dialogBox x ±intensity, yoyo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogBox.setAlpha(0); tweens: alpha→1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: y-=height, yoyo, ease:Bounce</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.flash(dur, 255,255,255)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// fx 컬럼에 예약어 입력  |  복합(Y끼리만): shake_screen|fade_out_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 파라미터 커스텀: shake_char:intensity=5,duration=300  (기본값 사용 시 예약어만 입력)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 배경 태그 → 파일명 매핑  |  파일명은 확장자 제외, Assets/Sprites/Backgrounds/ 경로 기준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// BGM 없는 이벤트는 행 비워두기  |  같은 BGM 유지 시 동일 파일명 복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// P : Player 고정 — 수정 불가  |  단축어는 대사 시트 char 컬럼에 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 닉네임: 비어있으면 캐릭터명 사용  |  ???처럼 미공개명 가능  |  런타임 변경: SaveManager.setFlag('cast_nick_A', 'Noa')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bounce_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 페이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 표정: b001 → Character_[캐릭터명]_001 자동 매핑  |  expr 공백 = 이전 표정 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// goto: 같은 시트 line_id | END | 다음 시트명  |  숫자 ID도 텍스트 서식으로 처리됨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외곽 지부 - 외부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외곽 지부 - 복도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외곽 지부 - 사무실</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.fadeOut → alpha 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: alpha 0↔1, yoyo, repeat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말 그대로 외각 지부입니다, 별 볼 일 없는 곳이죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.zoomTo(zoom, dur)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 복합 사용: Happy|Door  처럼 | 로 구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sprite.setTint → clearTint()</x:t>
+  </x:si>
+  <x:si>
     <x:t>저는 외곽 지부에 이전 관리자 노아(Noa)라고 합니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>bounce_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 페이드 인</x:t>
+    <x:t>tweens: scaleX/Y→scale, yoyo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fadeOut → onComplete: 다음 시트 로드</x:t>
   </x:si>
   <x:si>
     <x:t>화면 전체 진동</x:t>
@@ -44,604 +138,556 @@
     <x:t>캐릭터 페이드 아웃</x:t>
   </x:si>
   <x:si>
+    <x:t>fade_out</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_confirm</x:t>
+  </x:si>
+  <x:si>
     <x:t>Phaser3 구현</x:t>
   </x:si>
   <x:si>
-    <x:t>fade_out</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_confirm</x:t>
+    <x:t>speed=0.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이핑 속도 배속</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화창 페이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 순간 번쩍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>whiteout</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발화 캐릭터만 진동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>//관리자 캐릭터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pause_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>blackout</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[DIALOGUE]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그걸 왜 물어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flag_set</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내일도 잘 부탁해요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slow_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 미안해요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>day1_1_done</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shop_Open</x:t>
+  </x:si>
+  <x:si>
+    <x:t>player_rude</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ CAST ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flag_check</x:t>
   </x:si>
   <x:si>
     <x:t>zoom_out</x:t>
   </x:si>
   <x:si>
+    <x:t>repeat=2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pan_camera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화창 페이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 페이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tint_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shake_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 암전 후 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왼쪽에서 슬라이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 화이트아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 강조 확대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flash_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_sad_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_cancel</x:t>
+  </x:si>
+  <x:si>
     <x:t>화면 페이드 아웃</x:t>
   </x:si>
   <x:si>
-    <x:t>sfx_sad_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flash_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_cancel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>shake_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>왼쪽에서 슬라이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tint_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 페이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>repeat=2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 암전 후 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>pan_camera</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 화이트아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 강조 확대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화창 페이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>pause_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slow_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>blackout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발화 캐릭터만 진동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 순간 번쩍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flag_set</x:t>
-  </x:si>
-  <x:si>
-    <x:t>//관리자 캐릭터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>whiteout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내일도 잘 부탁해요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 미안해요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>day1_1_done</x:t>
-  </x:si>
-  <x:si>
-    <x:t>speed=0.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화창 페이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이핑 속도 배속</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[DIALOGUE]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그걸 왜 물어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>player_rude</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ CAST ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shop_Open</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flag_check</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// sfx: SFX 탭 별칭 (복합: Happy|Beep)  |  fx: FX 탭 예약어 (복합: shake_char|fade_out, 파라미터: shake_char:intensity=5)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 파라미터 커스텀: shake_char:intensity=5,duration=300  (기본값 사용 시 예약어만 입력)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sprite.x+=dist; tweens: x-=dist, alpha→1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sprite.x-=dist; tweens: x+=dist, alpha→1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// BGM 없는 이벤트는 행 비워두기  |  같은 BGM 유지 시 동일 파일명 복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: y-=height, yoyo, ease:Bounce</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: dialogBox x ±intensity, yoyo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogBox.setAlpha(0); tweens: alpha→1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.flash(dur, 255,255,255)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// target — screen: 카메라  |  char: 현재 발화 캐릭터  |  ui: 대화창  |  all: 전체</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 표정: b001 → Character_[캐릭터명]_001 자동 매핑  |  expr 공백 = 이전 표정 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// goto: 같은 시트 line_id | END | 다음 시트명  |  숫자 ID도 텍스트 서식으로 처리됨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// P : Player 고정 — 수정 불가  |  단축어는 대사 시트 char 컬럼에 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 닉네임: 비어있으면 캐릭터명 사용  |  ???처럼 미공개명 가능  |  런타임 변경: SaveManager.setFlag('cast_nick_A', 'Noa')</x:t>
+    <x:t>cameras.main.fadeOut(dur, r, g, b)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무튼, 새롭게 외각 지부 관리자로 부임하신 것을 축하드립니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: x ±intensity, yoyo, repeat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: dialogBox alpha 0.2→1, yoyo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.flash(dur, r, g, b)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 별칭을 대사 시트 sfx 컬럼에 입력 — 파일명 자동 매핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogManager.pauseTyping(duration)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM 파일명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cancel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상점 해금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬픈 반응</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이핑 루프</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씬 전환 연출</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부임이라니?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반갑습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화창 진동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX 파일명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>screen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Beep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UI 취소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shock</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템 알림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ FX ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Happy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Door</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 열림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>expr</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그저 그랬어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zoom_in</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카메라 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>line_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ BG ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외곽 지부?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>choice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경 파일명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shop_In</x:t>
+  </x:si>
+  <x:si>
+    <x:t>target</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카메라 줌 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화창 번쩍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>speed=2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 바운스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Player</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Day_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ BGM ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ SFX ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 파라미터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>goto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fade_in</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Typing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UI 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Confirm</x:t>
   </x:si>
   <x:si>
     <x:t>1일차 시작</x:t>
   </x:si>
   <x:si>
-    <x:t>Confirm</x:t>
-  </x:si>
-  <x:si>
     <x:t>충격/놀람</x:t>
   </x:si>
   <x:si>
     <x:t>기쁜 반응</x:t>
   </x:si>
   <x:si>
-    <x:t>Typing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UI 확인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이핑 루프</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Happy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반갑습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX 파일명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Door</x:t>
-  </x:si>
-  <x:si>
-    <x:t>screen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UI 취소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화창 진동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Beep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이벤트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상점 해금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM 파일명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 열림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cancel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shock</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시스템 알림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씬 전환 연출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬픈 반응</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ FX ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부임이라니?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>choice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>goto</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카메라 줌 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>target</x:t>
-  </x:si>
-  <x:si>
-    <x:t>expr</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 바운스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화창 번쩍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shop_In</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zoom_in</x:t>
-  </x:si>
-  <x:si>
-    <x:t>text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>speed=2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Day_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 파라미터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fade_in</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카메라 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그저 그랬어.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>line_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Player</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ BGM ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ SFX ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외곽 지부?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogManager.setTypingSpeed(speed)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.shake(dur, intensity)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.fadeIn(dur, r, g, b)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: x ±intensity, yoyo, repeat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogManager.pauseTyping(duration)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.fadeOut(dur, r, g, b)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.flash(dur, r, g, b)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무튼, 새롭게 외각 지부 관리자로 부임하신 것을 축하드립니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: dialogBox alpha 0.2→1, yoyo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 별칭을 대사 시트 sfx 컬럼에 입력 — 파일명 자동 매핑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// fx 컬럼에 예약어 입력  |  복합(Y끼리만): shake_screen|fade_out_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.zoomTo(zoom, dur)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sprite.setTint → clearTint()</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.fadeOut → alpha 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 복합 사용: Happy|Door  처럼 | 로 구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fadeOut → onComplete: 다음 시트 로드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말 그대로 외각 지부입니다, 별 볼 일 없는 곳이죠.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: scaleX/Y→scale, yoyo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: alpha 0↔1, yoyo, repeat</x:t>
-  </x:si>
-  <x:si>
     <x:t>B</x:t>
   </x:si>
   <x:si>
+    <x:t>L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>K</x:t>
+  </x:si>
+  <x:si>
     <x:t>C</x:t>
   </x:si>
   <x:si>
-    <x:t>O</x:t>
+    <x:t>M</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T</x:t>
+  </x:si>
+  <x:si>
+    <x:t>003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I</x:t>
+  </x:si>
+  <x:si>
+    <x:t>002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메모</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단축어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R</x:t>
   </x:si>
   <x:si>
     <x:t>비고</x:t>
   </x:si>
   <x:si>
-    <x:t>003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???</x:t>
-  </x:si>
-  <x:si>
-    <x:t>002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F</x:t>
-  </x:si>
-  <x:si>
-    <x:t>K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단축어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P</x:t>
+    <x:t>1</x:t>
   </x:si>
   <x:si>
     <x:t>H</x:t>
   </x:si>
   <x:si>
-    <x:t>A</x:t>
+    <x:t>N</x:t>
   </x:si>
   <x:si>
     <x:t>G</x:t>
   </x:si>
   <x:si>
-    <x:t>R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메모</x:t>
-  </x:si>
-  <x:si>
     <x:t>D</x:t>
   </x:si>
   <x:si>
-    <x:t>030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J</x:t>
-  </x:si>
-  <x:si>
     <x:t>E</x:t>
   </x:si>
   <x:si>
-    <x:t>I</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>001</x:t>
+    <x:t>Sad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S</x:t>
   </x:si>
   <x:si>
     <x:t>예약어</x:t>
   </x:si>
   <x:si>
+    <x:t>ui</x:t>
+  </x:si>
+  <x:si>
+    <x:t>all</x:t>
+  </x:si>
+  <x:si>
     <x:t>fx</x:t>
   </x:si>
   <x:si>
-    <x:t>Sad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ui</x:t>
-  </x:si>
-  <x:si>
-    <x:t>all</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S</x:t>
-  </x:si>
-  <x:si>
     <x:t>009</x:t>
   </x:si>
   <x:si>
     <x:t>010</x:t>
   </x:si>
   <x:si>
+    <x:t>007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Noa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q</x:t>
+  </x:si>
+  <x:si>
+    <x:t>006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>004</x:t>
+  </x:si>
+  <x:si>
     <x:t>008</x:t>
   </x:si>
   <x:si>
-    <x:t>006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>007</x:t>
-  </x:si>
-  <x:si>
     <x:t>END</x:t>
   </x:si>
   <x:si>
-    <x:t>Q</x:t>
-  </x:si>
-  <x:si>
-    <x:t>004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복합</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Noa</x:t>
+    <x:t>bgm_calm_morning</x:t>
   </x:si>
   <x:si>
     <x:t>textbox_fade_out</x:t>
   </x:si>
   <x:si>
-    <x:t>bgm_calm_morning</x:t>
+    <x:t>타이핑 일시 정지 (극적 침묵)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 인수인계를 시작하겠습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상점 입장 (동일 유지 시 복사)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음. . . 뭐, 상관 없나.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 색조 (분노/상태이상)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>── 화면 전체 (screen)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천천히 배우면 될 거라 생각합니다.</x:t>
   </x:si>
   <x:si>
     <x:t>── 캐릭터 단독 (char)</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 색조 (분노/상태이상)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상점 입장 (동일 유지 시 복사)</x:t>
-  </x:si>
-  <x:si>
     <x:t>── 대화창 / UI (ui)</x:t>
   </x:si>
   <x:si>
-    <x:t>그럼 인수인계를 시작하겠습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>── 화면 전체 (screen)</x:t>
-  </x:si>
-  <x:si>
     <x:t>scene_transition</x:t>
   </x:si>
   <x:si>
-    <x:t>타이핑 일시 정지 (극적 침묵)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천천히 배우면 될 거라 생각합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음. . . 뭐, 상관 없나.</x:t>
-  </x:si>
-  <x:si>
     <x:t>tweens: dialogBox alpha→0</x:t>
   </x:si>
   <x:si>
+    <x:t>intensity=3, duration=300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: x-=dist, alpha→0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>color=ffffff, duration=200</x:t>
+  </x:si>
+  <x:si>
     <x:t>// 이벤트 시트명과 동일하게 작성 — 자동 매핑</x:t>
   </x:si>
   <x:si>
+    <x:t>intensity=5, duration=300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scale=1.15, duration=200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.pan(x, y, dur)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 플레이어 고정 — 초상화 없음, 수정 불가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=300, distance=200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>color=ff4444, duration=200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=400, color=000000</x:t>
+  </x:si>
+  <x:si>
     <x:t>tweens: x+=dist, alpha→0</x:t>
   </x:si>
   <x:si>
     <x:t>intensity=3, duration=200</x:t>
   </x:si>
   <x:si>
-    <x:t>scale=1.15, duration=200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=300, distance=200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>intensity=5, duration=300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>color=ffffff, duration=200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=400, color=000000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.pan(x, y, dur)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>intensity=3, duration=300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: x-=dist, alpha→0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>color=ff4444, duration=200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 플레이어 고정 — 초상화 없음, 수정 불가</x:t>
+    <x:t>sfx_door_open</x:t>
+  </x:si>
+  <x:si>
+    <x:t>별칭 (sfx 컬럼에 입력)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bgm_shop_theme</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 ID (시트명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=250</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_shock_001</x:t>
   </x:si>
   <x:si>
     <x:t>duration=300</x:t>
   </x:si>
   <x:si>
-    <x:t>sfx_shock_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bgm_shop_theme</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_door_open</x:t>
+    <x:t>그렇군요... 잘 쉬세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카메라 줌 아웃 (원복)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flash_screen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: alpha→1</x:t>
   </x:si>
   <x:si>
     <x:t>slide_in_right</x:t>
@@ -650,97 +696,88 @@
     <x:t>sfx_happy_001</x:t>
   </x:si>
   <x:si>
-    <x:t>이벤트 ID (시트명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=250</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별칭 (sfx 컬럼에 입력)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flash_screen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렇군요... 잘 쉬세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카메라 줌 아웃 (원복)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: alpha→1</x:t>
+    <x:t>duration=150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_typing_loop</x:t>
   </x:si>
   <x:si>
     <x:t>fade_out_char</x:t>
   </x:si>
   <x:si>
+    <x:t>닉네임 (대화창 표시명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>speed_up_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>textbox_flash</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 왼쪽 슬라이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slide_in_left</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_beep_alert</x:t>
+  </x:si>
+  <x:si>
     <x:t>fade_in_char</x:t>
   </x:si>
   <x:si>
     <x:t>shake_screen</x:t>
   </x:si>
   <x:si>
+    <x:t>캐릭터 오른쪽 슬라이드 아웃</x:t>
+  </x:si>
+  <x:si>
     <x:t>오른쪽에서 슬라이드 인</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 오른쪽 슬라이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>textbox_flash</x:t>
+    <x:t>tweens: alpha→0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slide_out_right</x:t>
   </x:si>
   <x:si>
     <x:t>타이핑 속도 감속 (강조)</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 왼쪽 슬라이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: alpha→0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slide_out_right</x:t>
-  </x:si>
-  <x:si>
-    <x:t>닉네임 (대화창 표시명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_typing_loop</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slide_in_left</x:t>
-  </x:si>
-  <x:si>
-    <x:t>speed_up_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_beep_alert</x:t>
-  </x:si>
-  <x:si>
     <x:t>slide_out_left</x:t>
   </x:si>
   <x:si>
-    <x:t>duration=150</x:t>
+    <x:t>duration=500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background003</x:t>
   </x:si>
   <x:si>
     <x:t>scale_up_char</x:t>
   </x:si>
   <x:si>
+    <x:t>캐릭터 번쩍 (피격/강조)</x:t>
+  </x:si>
+  <x:si>
     <x:t>오늘 하루는 어떠셨나요?</x:t>
   </x:si>
   <x:si>
-    <x:t>duration=500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 번쩍 (피격/강조)</x:t>
+    <x:t>textbox_shake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>── 전체 동시 (all)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태그 (bg 컬럼에 입력)</x:t>
   </x:si>
   <x:si>
     <x:t>textbox_fade_in</x:t>
   </x:si>
   <x:si>
-    <x:t>── 전체 동시 (all)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>textbox_shake</x:t>
+    <x:t>Background001</x:t>
   </x:si>
   <x:si>
     <x:t>height=20, duration=400</x:t>
@@ -749,10 +786,10 @@
     <x:t>x=0, y=0, duration=500</x:t>
   </x:si>
   <x:si>
+    <x:t>//관리자 캐릭터가 이름을 공개하기 이전.</x:t>
+  </x:si>
+  <x:si>
     <x:t>이런, 아무것도 기억나지 않으신가보네요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>//관리자 캐릭터가 이름을 공개하기 이전.</x:t>
   </x:si>
   <x:si>
     <x:t>zoom=1.2, duration=300</x:t>
@@ -1643,28 +1680,6 @@
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
           <x:name val="Malgun Gothic"/>
-          <x:sz val="13"/>
-          <x:color rgb="ffffe066"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Malgun Gothic"/>
-          <x:sz val="13"/>
-          <x:color rgb="ffffe066"/>
-          <x:b val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Malgun Gothic"/>
           <x:sz val="10"/>
           <x:color rgb="ffffe066"/>
           <x:b val="1"/>
@@ -1720,6 +1735,28 @@
           <x:name val="Malgun Gothic"/>
           <x:sz val="10"/>
           <x:color rgb="ffffe066"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Malgun Gothic"/>
+          <x:sz val="13"/>
+          <x:color rgb="ffffe066"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Malgun Gothic"/>
+          <x:sz val="13"/>
+          <x:color rgb="ffffe066"/>
+          <x:b val="1"/>
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -1763,13 +1800,13 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="ff1e1e1e"/>
+        <x:fgColor rgb="ff131313"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="ff131313"/>
+        <x:fgColor rgb="ff1e1e1e"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -1837,7 +1874,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="137">
+  <x:cellXfs count="140">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -2727,7 +2764,43 @@
     <x:xf numFmtId="49" fontId="42" fillId="5" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="49" fillId="7" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="11" fillId="7" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="49" fillId="8" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="50" fillId="8" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="35" fillId="8" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="51" fillId="8" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="48" fillId="7" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="50" fillId="8" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="35" fillId="8" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="52" fillId="8" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2736,37 +2809,10 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="11" fillId="8" borderId="0" xfId="0" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="11" fillId="7" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="50" fillId="7" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="51" fillId="7" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="35" fillId="7" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="52" fillId="7" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="48" fillId="8" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="51" fillId="7" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="49" fontId="35" fillId="7" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="21" fillId="8" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -3464,88 +3510,88 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
-      <x:c r="A1" s="123" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B1" s="124"/>
-      <x:c r="C1" s="125"/>
+      <x:c r="A1" s="135" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B1" s="136"/>
+      <x:c r="C1" s="137"/>
       <x:c r="D1" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
-      <x:c r="A2" s="126" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B2" s="126"/>
-      <x:c r="C2" s="126"/>
+      <x:c r="A2" s="138" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B2" s="138"/>
+      <x:c r="C2" s="138"/>
       <x:c r="D2" s="3"/>
     </x:row>
     <x:row r="3" spans="1:4" ht="16" customHeight="1">
-      <x:c r="A3" s="126" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B3" s="126"/>
-      <x:c r="C3" s="126"/>
+      <x:c r="A3" s="138" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B3" s="138"/>
+      <x:c r="C3" s="138"/>
       <x:c r="D3" s="3"/>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="4" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>129</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D4" s="6" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="7" t="s">
-        <x:v>137</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B5" s="8" t="s">
-        <x:v>102</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C5" s="9" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D5" s="9"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="10" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B6" s="11" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C6" s="12" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>166</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="13" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="s">
-        <x:v>175</x:v>
-      </x:c>
       <x:c r="C7" s="11" t="s">
-        <x:v>242</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D7" s="15" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="10" t="s">
-        <x:v>127</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="12"/>
@@ -3553,7 +3599,7 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="13" t="s">
-        <x:v>146</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B9" s="14"/>
       <x:c r="C9" s="15"/>
@@ -3561,7 +3607,7 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="10" t="s">
-        <x:v>150</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="12"/>
@@ -3569,7 +3615,7 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="13" t="s">
-        <x:v>134</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B11" s="14"/>
       <x:c r="C11" s="15"/>
@@ -3577,7 +3623,7 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="10" t="s">
-        <x:v>140</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="12"/>
@@ -3585,7 +3631,7 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="13" t="s">
-        <x:v>138</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B13" s="14"/>
       <x:c r="C13" s="15"/>
@@ -3593,7 +3639,7 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="10" t="s">
-        <x:v>151</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B14" s="11"/>
       <x:c r="C14" s="12"/>
@@ -3601,7 +3647,7 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="13" t="s">
-        <x:v>149</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B15" s="14"/>
       <x:c r="C15" s="15"/>
@@ -3609,7 +3655,7 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="10" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="12"/>
@@ -3617,7 +3663,7 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="13" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B17" s="14"/>
       <x:c r="C17" s="15"/>
@@ -3625,7 +3671,7 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="10" t="s">
-        <x:v>148</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="12"/>
@@ -3633,7 +3679,7 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B19" s="14"/>
       <x:c r="C19" s="15"/>
@@ -3641,7 +3687,7 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="10" t="s">
-        <x:v>128</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="12"/>
@@ -3649,7 +3695,7 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="13" t="s">
-        <x:v>137</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B21" s="14"/>
       <x:c r="C21" s="15"/>
@@ -3657,7 +3703,7 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="10" t="s">
-        <x:v>169</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B22" s="11"/>
       <x:c r="C22" s="12"/>
@@ -3665,7 +3711,7 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="13" t="s">
-        <x:v>141</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B23" s="14"/>
       <x:c r="C23" s="15"/>
@@ -3673,7 +3719,7 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="10" t="s">
-        <x:v>161</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="12"/>
@@ -3681,7 +3727,7 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="13" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B25" s="14"/>
       <x:c r="C25" s="15"/>
@@ -3730,6 +3776,120 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="SheetBG">
+    <x:tabColor rgb="ff44bbff"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:D10"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" style="2" customWidth="1"/>
+    <x:col min="2" max="2" width="30" style="2" customWidth="1"/>
+    <x:col min="3" max="3" width="34" style="2" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:4" ht="19.25">
+      <x:c r="A1" s="135" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B1" s="136"/>
+      <x:c r="C1" s="137"/>
+      <x:c r="D1" s="3"/>
+    </x:row>
+    <x:row r="2" spans="1:4" ht="16" customHeight="1">
+      <x:c r="A2" s="138" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B2" s="138"/>
+      <x:c r="C2" s="138"/>
+      <x:c r="D2" s="3"/>
+    </x:row>
+    <x:row r="3" spans="1:4" ht="16" customHeight="1">
+      <x:c r="A3" s="138" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="138"/>
+      <x:c r="C3" s="138"/>
+      <x:c r="D3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:4">
+      <x:c r="A4" s="16" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D4" s="3"/>
+    </x:row>
+    <x:row r="5" spans="1:4">
+      <x:c r="A5" s="17" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B5" s="18" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C5" s="19" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D5" s="3"/>
+    </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="20" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="C6" s="22" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D6" s="3"/>
+    </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="17" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B7" s="18" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="C7" s="19" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D7" s="3"/>
+    </x:row>
+    <x:row r="8" spans="1:4">
+      <x:c r="A8" s="20"/>
+      <x:c r="B8" s="21"/>
+      <x:c r="C8" s="22"/>
+      <x:c r="D8" s="3"/>
+    </x:row>
+    <x:row r="9" spans="1:4">
+      <x:c r="A9" s="17"/>
+      <x:c r="B9" s="18"/>
+      <x:c r="C9" s="23"/>
+      <x:c r="D9" s="3"/>
+    </x:row>
+    <x:row r="10" spans="1:4">
+      <x:c r="A10" s="20"/>
+      <x:c r="B10" s="21"/>
+      <x:c r="C10" s="24"/>
+      <x:c r="D10" s="3"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="3">
+    <x:mergeCell ref="A1:C1"/>
+    <x:mergeCell ref="A2:C2"/>
+    <x:mergeCell ref="A3:C3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet2">
     <x:tabColor rgb="ff5dd8f0"/>
   </x:sheetPr>
@@ -3742,74 +3902,74 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
-      <x:c r="A1" s="123" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B1" s="124"/>
-      <x:c r="C1" s="125"/>
+      <x:c r="A1" s="135" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B1" s="136"/>
+      <x:c r="C1" s="137"/>
       <x:c r="D1" s="3"/>
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
-      <x:c r="A2" s="126" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="B2" s="126"/>
-      <x:c r="C2" s="126"/>
+      <x:c r="A2" s="138" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B2" s="138"/>
+      <x:c r="C2" s="138"/>
       <x:c r="D2" s="3"/>
     </x:row>
     <x:row r="3" spans="1:4" ht="16" customHeight="1">
-      <x:c r="A3" s="126" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B3" s="126"/>
-      <x:c r="C3" s="126"/>
+      <x:c r="A3" s="138" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B3" s="138"/>
+      <x:c r="C3" s="138"/>
       <x:c r="D3" s="3"/>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="16" t="s">
-        <x:v>208</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>129</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="17" t="s">
-        <x:v>95</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B5" s="18" t="s">
-        <x:v>177</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C5" s="19" t="s">
-        <x:v>58</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="20" t="s">
-        <x:v>42</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>204</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C6" s="22" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="17" t="s">
-        <x:v>91</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B7" s="18" t="s">
-        <x:v>204</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C7" s="19" t="s">
-        <x:v>180</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
     </x:row>
@@ -4202,7 +4362,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet3">
     <x:tabColor rgb="ff44ccaa"/>
@@ -4216,134 +4376,134 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
-      <x:c r="A1" s="123" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B1" s="124"/>
-      <x:c r="C1" s="125"/>
+      <x:c r="A1" s="135" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B1" s="136"/>
+      <x:c r="C1" s="137"/>
       <x:c r="D1" s="3"/>
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
-      <x:c r="A2" s="126" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B2" s="126"/>
-      <x:c r="C2" s="126"/>
+      <x:c r="A2" s="138" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B2" s="138"/>
+      <x:c r="C2" s="138"/>
       <x:c r="D2" s="3"/>
     </x:row>
     <x:row r="3" spans="1:4" ht="16" customHeight="1">
-      <x:c r="A3" s="126" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="B3" s="126"/>
-      <x:c r="C3" s="126"/>
+      <x:c r="A3" s="138" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B3" s="138"/>
+      <x:c r="C3" s="138"/>
       <x:c r="D3" s="3"/>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="25" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>67</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>129</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="26" t="s">
-        <x:v>65</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B5" s="18" t="s">
-        <x:v>207</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C5" s="19" t="s">
-        <x:v>61</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="27" t="s">
-        <x:v>158</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C6" s="22" t="s">
-        <x:v>81</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="26" t="s">
-        <x:v>78</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B7" s="18" t="s">
-        <x:v>203</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C7" s="19" t="s">
-        <x:v>60</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="27" t="s">
-        <x:v>68</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B8" s="21" t="s">
-        <x:v>205</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C8" s="22" t="s">
-        <x:v>76</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="26" t="s">
-        <x:v>72</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B9" s="18" t="s">
-        <x:v>229</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="27" t="s">
-        <x:v>62</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B10" s="21" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C10" s="22" t="s">
-        <x:v>64</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="26" t="s">
-        <x:v>59</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B11" s="18" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="19" t="s">
-        <x:v>63</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D11" s="3"/>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="27" t="s">
-        <x:v>77</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B12" s="21" t="s">
-        <x:v>13</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C12" s="22" t="s">
-        <x:v>70</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D12" s="3"/>
     </x:row>
@@ -4736,7 +4896,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet4">
     <x:tabColor rgb="ffbb88ff"/>
@@ -4753,663 +4913,663 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="19.25">
-      <x:c r="A1" s="123" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B1" s="124"/>
-      <x:c r="C1" s="124"/>
-      <x:c r="D1" s="124"/>
-      <x:c r="E1" s="124"/>
-      <x:c r="F1" s="125"/>
+      <x:c r="A1" s="135" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B1" s="136"/>
+      <x:c r="C1" s="136"/>
+      <x:c r="D1" s="136"/>
+      <x:c r="E1" s="136"/>
+      <x:c r="F1" s="137"/>
     </x:row>
     <x:row r="2" spans="1:6" ht="16" customHeight="1">
-      <x:c r="A2" s="126" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="B2" s="126"/>
-      <x:c r="C2" s="126"/>
-      <x:c r="D2" s="126"/>
-      <x:c r="E2" s="126"/>
-      <x:c r="F2" s="126"/>
+      <x:c r="A2" s="138" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B2" s="138"/>
+      <x:c r="C2" s="138"/>
+      <x:c r="D2" s="138"/>
+      <x:c r="E2" s="138"/>
+      <x:c r="F2" s="138"/>
     </x:row>
     <x:row r="3" spans="1:6" ht="16" customHeight="1">
-      <x:c r="A3" s="126" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B3" s="126"/>
-      <x:c r="C3" s="126"/>
-      <x:c r="D3" s="126"/>
-      <x:c r="E3" s="126"/>
-      <x:c r="F3" s="126"/>
+      <x:c r="A3" s="138" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B3" s="138"/>
+      <x:c r="C3" s="138"/>
+      <x:c r="D3" s="138"/>
+      <x:c r="E3" s="138"/>
+      <x:c r="F3" s="138"/>
     </x:row>
     <x:row r="4" spans="1:6" ht="16" customHeight="1">
-      <x:c r="A4" s="126" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B4" s="126"/>
-      <x:c r="C4" s="126"/>
-      <x:c r="D4" s="126"/>
-      <x:c r="E4" s="126"/>
-      <x:c r="F4" s="126"/>
+      <x:c r="A4" s="138" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="138"/>
+      <x:c r="C4" s="138"/>
+      <x:c r="D4" s="138"/>
+      <x:c r="E4" s="138"/>
+      <x:c r="F4" s="138"/>
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" s="30" t="s">
-        <x:v>156</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B5" s="31" t="s">
-        <x:v>87</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C5" s="16" t="s">
-        <x:v>96</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>154</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F5" s="32" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="28" customHeight="1">
-      <x:c r="A6" s="127" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="B6" s="127"/>
-      <x:c r="C6" s="127"/>
-      <x:c r="D6" s="127"/>
-      <x:c r="E6" s="127"/>
-      <x:c r="F6" s="127"/>
+      <x:c r="A6" s="139" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B6" s="139"/>
+      <x:c r="C6" s="139"/>
+      <x:c r="D6" s="139"/>
+      <x:c r="E6" s="139"/>
+      <x:c r="F6" s="139"/>
     </x:row>
     <x:row r="7" spans="1:6" ht="28" customHeight="1">
       <x:c r="A7" s="33" t="s">
-        <x:v>217</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B7" s="34" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C7" s="35" t="s">
-        <x:v>198</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D7" s="36" t="s">
-        <x:v>4</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E7" s="37" t="s">
-        <x:v>108</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F7" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="28" customHeight="1">
       <x:c r="A8" s="39" t="s">
-        <x:v>211</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B8" s="40" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C8" s="41" t="s">
-        <x:v>195</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D8" s="42" t="s">
-        <x:v>28</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E8" s="43" t="s">
-        <x:v>113</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F8" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="28" customHeight="1">
       <x:c r="A9" s="33" t="s">
-        <x:v>7</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B9" s="34" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C9" s="35" t="s">
-        <x:v>196</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D9" s="36" t="s">
-        <x:v>10</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E9" s="37" t="s">
-        <x:v>112</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F9" s="45" t="s">
-        <x:v>143</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="28" customHeight="1">
       <x:c r="A10" s="39" t="s">
-        <x:v>97</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B10" s="40" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C10" s="41" t="s">
-        <x:v>196</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D10" s="42" t="s">
-        <x:v>3</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E10" s="43" t="s">
-        <x:v>109</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F10" s="46" t="s">
-        <x:v>143</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="28" customHeight="1">
       <x:c r="A11" s="33" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B11" s="34" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B11" s="34" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="C11" s="35" t="s">
-        <x:v>243</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D11" s="36" t="s">
-        <x:v>86</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E11" s="37" t="s">
-        <x:v>118</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F11" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="28" customHeight="1">
       <x:c r="A12" s="39" t="s">
-        <x:v>9</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B12" s="40" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C12" s="41" t="s">
-        <x:v>244</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="D12" s="42" t="s">
-        <x:v>213</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="E12" s="43" t="s">
-        <x:v>118</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F12" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="28" customHeight="1">
       <x:c r="A13" s="33" t="s">
-        <x:v>20</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B13" s="34" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C13" s="35" t="s">
-        <x:v>240</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D13" s="36" t="s">
-        <x:v>98</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E13" s="37" t="s">
-        <x:v>197</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F13" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="28" customHeight="1">
-      <x:c r="A14" s="127" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="B14" s="127"/>
-      <x:c r="C14" s="127"/>
-      <x:c r="D14" s="127"/>
-      <x:c r="E14" s="127"/>
-      <x:c r="F14" s="127"/>
+      <x:c r="A14" s="139" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B14" s="139"/>
+      <x:c r="C14" s="139"/>
+      <x:c r="D14" s="139"/>
+      <x:c r="E14" s="139"/>
+      <x:c r="F14" s="139"/>
     </x:row>
     <x:row r="15" spans="1:6" ht="28" customHeight="1">
       <x:c r="A15" s="33" t="s">
-        <x:v>14</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B15" s="38" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C15" s="35" t="s">
-        <x:v>194</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D15" s="36" t="s">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E15" s="37" t="s">
-        <x:v>110</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F15" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="28" customHeight="1">
       <x:c r="A16" s="39" t="s">
-        <x:v>230</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B16" s="44" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C16" s="41" t="s">
-        <x:v>193</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D16" s="42" t="s">
-        <x:v>222</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E16" s="43" t="s">
-        <x:v>199</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="F16" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="28" customHeight="1">
       <x:c r="A17" s="33" t="s">
-        <x:v>224</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B17" s="38" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C17" s="35" t="s">
-        <x:v>193</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D17" s="36" t="s">
-        <x:v>219</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E17" s="37" t="s">
-        <x:v>190</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F17" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="28" customHeight="1">
       <x:c r="A18" s="39" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B18" s="44" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C18" s="41" t="s">
-        <x:v>193</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D18" s="42" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E18" s="43" t="s">
-        <x:v>47</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F18" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="28" customHeight="1">
       <x:c r="A19" s="33" t="s">
-        <x:v>206</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B19" s="38" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C19" s="35" t="s">
-        <x:v>193</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D19" s="36" t="s">
-        <x:v>218</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E19" s="37" t="s">
-        <x:v>46</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F19" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6" ht="28" customHeight="1">
       <x:c r="A20" s="39" t="s">
-        <x:v>215</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B20" s="44" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C20" s="41" t="s">
-        <x:v>202</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D20" s="42" t="s">
-        <x:v>5</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E20" s="43" t="s">
-        <x:v>223</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="F20" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6" ht="28" customHeight="1">
       <x:c r="A21" s="33" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B21" s="38" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C21" s="35" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="B21" s="38" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="C21" s="35" t="s">
-        <x:v>202</x:v>
-      </x:c>
       <x:c r="D21" s="36" t="s">
-        <x:v>17</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E21" s="37" t="s">
-        <x:v>214</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="F21" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6" ht="28" customHeight="1">
       <x:c r="A22" s="39" t="s">
-        <x:v>2</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="44" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C22" s="41" t="s">
-        <x:v>239</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="D22" s="42" t="s">
-        <x:v>89</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E22" s="43" t="s">
-        <x:v>49</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6" ht="28" customHeight="1">
       <x:c r="A23" s="33" t="s">
-        <x:v>12</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B23" s="38" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C23" s="35" t="s">
-        <x:v>18</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D23" s="36" t="s">
-        <x:v>235</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="E23" s="37" t="s">
-        <x:v>125</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F23" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6" ht="28" customHeight="1">
       <x:c r="A24" s="39" t="s">
-        <x:v>16</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B24" s="44" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C24" s="41" t="s">
-        <x:v>200</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D24" s="42" t="s">
-        <x:v>179</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E24" s="43" t="s">
-        <x:v>119</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F24" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6" ht="28" customHeight="1">
       <x:c r="A25" s="33" t="s">
-        <x:v>232</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B25" s="38" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C25" s="35" t="s">
-        <x:v>192</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D25" s="36" t="s">
-        <x:v>22</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E25" s="37" t="s">
-        <x:v>124</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F25" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="28" customHeight="1">
-      <x:c r="A26" s="127" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="B26" s="127"/>
-      <x:c r="C26" s="127"/>
-      <x:c r="D26" s="127"/>
-      <x:c r="E26" s="127"/>
-      <x:c r="F26" s="127"/>
+      <x:c r="A26" s="139" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B26" s="139"/>
+      <x:c r="C26" s="139"/>
+      <x:c r="D26" s="139"/>
+      <x:c r="E26" s="139"/>
+      <x:c r="F26" s="139"/>
     </x:row>
     <x:row r="27" spans="1:6" ht="28" customHeight="1">
       <x:c r="A27" s="33" t="s">
-        <x:v>238</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B27" s="47" t="s">
-        <x:v>159</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C27" s="35" t="s">
-        <x:v>191</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D27" s="36" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E27" s="37" t="s">
-        <x:v>50</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F27" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6" ht="28" customHeight="1">
       <x:c r="A28" s="39" t="s">
-        <x:v>220</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B28" s="48" t="s">
-        <x:v>159</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C28" s="41" t="s">
-        <x:v>231</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="D28" s="42" t="s">
-        <x:v>90</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E28" s="43" t="s">
-        <x:v>115</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F28" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6" ht="28" customHeight="1">
       <x:c r="A29" s="33" t="s">
-        <x:v>236</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B29" s="47" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C29" s="35" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D29" s="36" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="E29" s="37" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F29" s="45" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="C29" s="35" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D29" s="36" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E29" s="37" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F29" s="45" t="s">
-        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6" ht="28" customHeight="1">
       <x:c r="A30" s="39" t="s">
-        <x:v>176</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B30" s="48" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="C30" s="41" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D30" s="42" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E30" s="43" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F30" s="46" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="C30" s="41" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="D30" s="42" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E30" s="43" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F30" s="46" t="s">
-        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6" ht="28" customHeight="1">
       <x:c r="A31" s="33" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B31" s="47" t="s">
-        <x:v>159</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C31" s="35" t="s">
-        <x:v>234</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D31" s="36" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E31" s="37" t="s">
-        <x:v>111</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F31" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6" ht="28" customHeight="1">
       <x:c r="A32" s="39" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B32" s="48" t="s">
-        <x:v>159</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C32" s="41" t="s">
-        <x:v>94</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D32" s="42" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E32" s="43" t="s">
-        <x:v>107</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F32" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6" ht="28" customHeight="1">
       <x:c r="A33" s="33" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B33" s="47" t="s">
-        <x:v>159</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C33" s="35" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D33" s="36" t="s">
-        <x:v>221</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E33" s="37" t="s">
-        <x:v>107</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F33" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6" ht="28" customHeight="1">
-      <x:c r="A34" s="127" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="B34" s="127"/>
-      <x:c r="C34" s="127"/>
-      <x:c r="D34" s="127"/>
-      <x:c r="E34" s="127"/>
-      <x:c r="F34" s="127"/>
+      <x:c r="A34" s="139" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B34" s="139"/>
+      <x:c r="C34" s="139"/>
+      <x:c r="D34" s="139"/>
+      <x:c r="E34" s="139"/>
+      <x:c r="F34" s="139"/>
     </x:row>
     <x:row r="35" spans="1:6" ht="28" customHeight="1">
       <x:c r="A35" s="33" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B35" s="49" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="C35" s="35" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D35" s="36" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E35" s="37" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B35" s="49" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="C35" s="35" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="D35" s="36" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E35" s="37" t="s">
-        <x:v>120</x:v>
-      </x:c>
       <x:c r="F35" s="45" t="s">
-        <x:v>143</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6" ht="28" customHeight="1">
       <x:c r="A36" s="39" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B36" s="50" t="s">
-        <x:v>160</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C36" s="41" t="s">
-        <x:v>202</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D36" s="42" t="s">
-        <x:v>21</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E36" s="43" t="s">
-        <x:v>52</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F36" s="46" t="s">
-        <x:v>143</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6" ht="28" customHeight="1">
       <x:c r="A37" s="33" t="s">
-        <x:v>184</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B37" s="49" t="s">
-        <x:v>160</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C37" s="35" t="s">
-        <x:v>196</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D37" s="36" t="s">
-        <x:v>80</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E37" s="37" t="s">
-        <x:v>122</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F37" s="45" t="s">
-        <x:v>143</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -5852,7 +6012,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet6">
     <x:tabColor rgb="ff7fdd55"/>
@@ -5868,130 +6028,133 @@
     <x:col min="7" max="8" width="16" style="2" customWidth="1"/>
     <x:col min="9" max="9" width="12" style="2" customWidth="1"/>
     <x:col min="10" max="10" width="20" style="2" customWidth="1"/>
+    <x:col min="11" max="11" width="10" style="2" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="56" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B1" s="129"/>
-      <x:c r="C1" s="124"/>
-      <x:c r="D1" s="124"/>
-      <x:c r="E1" s="124"/>
-      <x:c r="F1" s="124"/>
-      <x:c r="G1" s="125"/>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B1" s="127"/>
+      <x:c r="C1" s="123"/>
+      <x:c r="D1" s="123"/>
+      <x:c r="E1" s="123"/>
+      <x:c r="F1" s="123"/>
+      <x:c r="G1" s="124"/>
       <x:c r="H1" s="56" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="I1" s="130"/>
-      <x:c r="J1" s="125"/>
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="I1" s="128"/>
+      <x:c r="J1" s="124"/>
       <x:c r="K1" s="3"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="16" customHeight="1">
-      <x:c r="A2" s="126" t="s">
+      <x:c r="A2" s="125" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B2" s="126"/>
-      <x:c r="C2" s="126"/>
-      <x:c r="D2" s="126"/>
-      <x:c r="E2" s="126"/>
-      <x:c r="F2" s="126"/>
-      <x:c r="G2" s="126"/>
-      <x:c r="H2" s="126"/>
-      <x:c r="I2" s="126"/>
-      <x:c r="J2" s="126"/>
+      <x:c r="B2" s="125"/>
+      <x:c r="C2" s="125"/>
+      <x:c r="D2" s="125"/>
+      <x:c r="E2" s="125"/>
+      <x:c r="F2" s="125"/>
+      <x:c r="G2" s="125"/>
+      <x:c r="H2" s="125"/>
+      <x:c r="I2" s="125"/>
+      <x:c r="J2" s="125"/>
       <x:c r="K2" s="3"/>
     </x:row>
     <x:row r="3" spans="1:11" ht="16" customHeight="1">
-      <x:c r="A3" s="126" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B3" s="126"/>
-      <x:c r="C3" s="126"/>
-      <x:c r="D3" s="126"/>
-      <x:c r="E3" s="126"/>
-      <x:c r="F3" s="126"/>
-      <x:c r="G3" s="126"/>
-      <x:c r="H3" s="126"/>
-      <x:c r="I3" s="126"/>
-      <x:c r="J3" s="126"/>
+      <x:c r="A3" s="125" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B3" s="125"/>
+      <x:c r="C3" s="125"/>
+      <x:c r="D3" s="125"/>
+      <x:c r="E3" s="125"/>
+      <x:c r="F3" s="125"/>
+      <x:c r="G3" s="125"/>
+      <x:c r="H3" s="125"/>
+      <x:c r="I3" s="125"/>
+      <x:c r="J3" s="125"/>
       <x:c r="K3" s="3"/>
     </x:row>
     <x:row r="4" spans="1:11" ht="16" customHeight="1">
-      <x:c r="A4" s="126" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B4" s="126"/>
-      <x:c r="C4" s="126"/>
-      <x:c r="D4" s="126"/>
-      <x:c r="E4" s="126"/>
-      <x:c r="F4" s="126"/>
-      <x:c r="G4" s="126"/>
-      <x:c r="H4" s="126"/>
-      <x:c r="I4" s="126"/>
-      <x:c r="J4" s="126"/>
+      <x:c r="A4" s="125" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="125"/>
+      <x:c r="C4" s="125"/>
+      <x:c r="D4" s="125"/>
+      <x:c r="E4" s="125"/>
+      <x:c r="F4" s="125"/>
+      <x:c r="G4" s="125"/>
+      <x:c r="H4" s="125"/>
+      <x:c r="I4" s="125"/>
+      <x:c r="J4" s="125"/>
       <x:c r="K4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:11">
-      <x:c r="A5" s="128" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B5" s="124"/>
-      <x:c r="C5" s="124"/>
-      <x:c r="D5" s="124"/>
-      <x:c r="E5" s="124"/>
-      <x:c r="F5" s="124"/>
-      <x:c r="G5" s="124"/>
-      <x:c r="H5" s="124"/>
-      <x:c r="I5" s="124"/>
-      <x:c r="J5" s="125"/>
+      <x:c r="A5" s="126" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B5" s="123"/>
+      <x:c r="C5" s="123"/>
+      <x:c r="D5" s="123"/>
+      <x:c r="E5" s="123"/>
+      <x:c r="F5" s="123"/>
+      <x:c r="G5" s="123"/>
+      <x:c r="H5" s="123"/>
+      <x:c r="I5" s="123"/>
+      <x:c r="J5" s="124"/>
       <x:c r="K5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="16" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C6" s="31" t="s">
-        <x:v>88</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>93</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E6" s="57" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F6" s="57" t="s">
-        <x:v>85</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G6" s="51" t="s">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H6" s="51" t="s">
-        <x:v>43</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I6" s="25" t="s">
-        <x:v>142</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="J6" s="30" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="K6" s="3"/>
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="K6" s="30" t="s">
+        <x:v>178</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="58" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B7" s="59" t="s">
-        <x:v>126</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C7" s="60" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D7" s="61" t="s">
-        <x:v>233</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="E7" s="62"/>
       <x:c r="F7" s="63"/>
@@ -5999,132 +6162,132 @@
       <x:c r="H7" s="64"/>
       <x:c r="I7" s="65"/>
       <x:c r="J7" s="66"/>
-      <x:c r="K7" s="3"/>
+      <x:c r="K7" s="66"/>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="67" t="s">
-        <x:v>132</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B8" s="68" t="s">
-        <x:v>137</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C8" s="69"/>
       <x:c r="D8" s="70" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E8" s="71" t="s">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F8" s="72" t="s">
-        <x:v>163</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G8" s="73"/>
       <x:c r="H8" s="73"/>
       <x:c r="I8" s="74"/>
       <x:c r="J8" s="75"/>
-      <x:c r="K8" s="3"/>
+      <x:c r="K8" s="75"/>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="58" t="s">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B9" s="59" t="s">
-        <x:v>137</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C9" s="76"/>
       <x:c r="D9" s="61" t="s">
-        <x:v>39</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E9" s="77" t="s">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F9" s="78" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G9" s="64"/>
       <x:c r="H9" s="64"/>
       <x:c r="I9" s="65"/>
       <x:c r="J9" s="66"/>
-      <x:c r="K9" s="3"/>
+      <x:c r="K9" s="66"/>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="67" t="s">
-        <x:v>163</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B10" s="68" t="s">
-        <x:v>126</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C10" s="79" t="s">
-        <x:v>132</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D10" s="70" t="s">
-        <x:v>212</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E10" s="80"/>
       <x:c r="F10" s="72" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G10" s="73"/>
       <x:c r="H10" s="73"/>
       <x:c r="I10" s="81" t="s">
-        <x:v>158</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="J10" s="75"/>
-      <x:c r="K10" s="3"/>
+      <x:c r="K10" s="75"/>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="58" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B11" s="59" t="s">
-        <x:v>126</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C11" s="60" t="s">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D11" s="61" t="s">
-        <x:v>33</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="62"/>
       <x:c r="F11" s="78" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G11" s="82" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H11" s="64"/>
       <x:c r="I11" s="65"/>
       <x:c r="J11" s="83" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="K11" s="3"/>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="K11" s="66"/>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="67" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B12" s="68" t="s">
-        <x:v>126</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C12" s="79" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D12" s="70" t="s">
-        <x:v>32</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E12" s="80"/>
       <x:c r="F12" s="72" t="s">
-        <x:v>168</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="G12" s="84" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="73"/>
       <x:c r="I12" s="74"/>
       <x:c r="J12" s="85" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="K12" s="3"/>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K12" s="75"/>
     </x:row>
     <x:row r="13" spans="1:11" ht="18" customHeight="1">
       <x:c r="A13" s="17"/>
@@ -6137,7 +6300,7 @@
       <x:c r="H13" s="52"/>
       <x:c r="I13" s="28"/>
       <x:c r="J13" s="53"/>
-      <x:c r="K13" s="3"/>
+      <x:c r="K13" s="66"/>
     </x:row>
     <x:row r="14" spans="1:11" ht="18" customHeight="1">
       <x:c r="A14" s="20"/>
@@ -6150,7 +6313,7 @@
       <x:c r="H14" s="54"/>
       <x:c r="I14" s="29"/>
       <x:c r="J14" s="55"/>
-      <x:c r="K14" s="3"/>
+      <x:c r="K14" s="75"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="18" customHeight="1">
       <x:c r="A15" s="17"/>
@@ -6163,7 +6326,7 @@
       <x:c r="H15" s="52"/>
       <x:c r="I15" s="28"/>
       <x:c r="J15" s="53"/>
-      <x:c r="K15" s="3"/>
+      <x:c r="K15" s="66"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="18" customHeight="1">
       <x:c r="A16" s="20"/>
@@ -6176,7 +6339,7 @@
       <x:c r="H16" s="54"/>
       <x:c r="I16" s="29"/>
       <x:c r="J16" s="55"/>
-      <x:c r="K16" s="3"/>
+      <x:c r="K16" s="75"/>
     </x:row>
     <x:row r="17" spans="1:11" ht="18" customHeight="1">
       <x:c r="A17" s="17"/>
@@ -6189,7 +6352,7 @@
       <x:c r="H17" s="52"/>
       <x:c r="I17" s="28"/>
       <x:c r="J17" s="53"/>
-      <x:c r="K17" s="3"/>
+      <x:c r="K17" s="66"/>
     </x:row>
     <x:row r="18" spans="1:11" ht="18" customHeight="1">
       <x:c r="A18" s="20"/>
@@ -6202,7 +6365,7 @@
       <x:c r="H18" s="54"/>
       <x:c r="I18" s="29"/>
       <x:c r="J18" s="55"/>
-      <x:c r="K18" s="3"/>
+      <x:c r="K18" s="75"/>
     </x:row>
     <x:row r="19" spans="1:11" ht="18" customHeight="1">
       <x:c r="A19" s="17"/>
@@ -6215,7 +6378,7 @@
       <x:c r="H19" s="52"/>
       <x:c r="I19" s="28"/>
       <x:c r="J19" s="53"/>
-      <x:c r="K19" s="3"/>
+      <x:c r="K19" s="66"/>
     </x:row>
     <x:row r="20" spans="1:11" ht="18" customHeight="1">
       <x:c r="A20" s="20"/>
@@ -6228,7 +6391,7 @@
       <x:c r="H20" s="54"/>
       <x:c r="I20" s="29"/>
       <x:c r="J20" s="55"/>
-      <x:c r="K20" s="3"/>
+      <x:c r="K20" s="75"/>
     </x:row>
     <x:row r="21" spans="1:11" ht="18" customHeight="1">
       <x:c r="A21" s="17"/>
@@ -6241,7 +6404,7 @@
       <x:c r="H21" s="52"/>
       <x:c r="I21" s="28"/>
       <x:c r="J21" s="53"/>
-      <x:c r="K21" s="3"/>
+      <x:c r="K21" s="66"/>
     </x:row>
     <x:row r="22" spans="1:11" ht="18" customHeight="1">
       <x:c r="A22" s="20"/>
@@ -6254,7 +6417,7 @@
       <x:c r="H22" s="54"/>
       <x:c r="I22" s="29"/>
       <x:c r="J22" s="55"/>
-      <x:c r="K22" s="3"/>
+      <x:c r="K22" s="75"/>
     </x:row>
     <x:row r="23" spans="1:11" ht="18" customHeight="1">
       <x:c r="A23" s="17"/>
@@ -6267,7 +6430,7 @@
       <x:c r="H23" s="52"/>
       <x:c r="I23" s="28"/>
       <x:c r="J23" s="53"/>
-      <x:c r="K23" s="3"/>
+      <x:c r="K23" s="66"/>
     </x:row>
     <x:row r="24" spans="1:11" ht="18" customHeight="1">
       <x:c r="A24" s="20"/>
@@ -6280,7 +6443,7 @@
       <x:c r="H24" s="54"/>
       <x:c r="I24" s="29"/>
       <x:c r="J24" s="55"/>
-      <x:c r="K24" s="3"/>
+      <x:c r="K24" s="75"/>
     </x:row>
     <x:row r="25" spans="1:11" ht="18" customHeight="1">
       <x:c r="A25" s="17"/>
@@ -6293,7 +6456,7 @@
       <x:c r="H25" s="52"/>
       <x:c r="I25" s="28"/>
       <x:c r="J25" s="53"/>
-      <x:c r="K25" s="3"/>
+      <x:c r="K25" s="66"/>
     </x:row>
     <x:row r="26" spans="1:11" ht="18" customHeight="1">
       <x:c r="A26" s="20"/>
@@ -6306,7 +6469,7 @@
       <x:c r="H26" s="54"/>
       <x:c r="I26" s="29"/>
       <x:c r="J26" s="55"/>
-      <x:c r="K26" s="3"/>
+      <x:c r="K26" s="75"/>
     </x:row>
     <x:row r="27" spans="1:11" ht="18" customHeight="1">
       <x:c r="A27" s="17"/>
@@ -6319,7 +6482,7 @@
       <x:c r="H27" s="52"/>
       <x:c r="I27" s="28"/>
       <x:c r="J27" s="53"/>
-      <x:c r="K27" s="3"/>
+      <x:c r="K27" s="66"/>
     </x:row>
     <x:row r="28" spans="1:11" ht="18" customHeight="1">
       <x:c r="A28" s="20"/>
@@ -6332,7 +6495,7 @@
       <x:c r="H28" s="54"/>
       <x:c r="I28" s="29"/>
       <x:c r="J28" s="55"/>
-      <x:c r="K28" s="3"/>
+      <x:c r="K28" s="75"/>
     </x:row>
     <x:row r="29" spans="1:11" ht="18" customHeight="1">
       <x:c r="A29" s="17"/>
@@ -6345,7 +6508,7 @@
       <x:c r="H29" s="52"/>
       <x:c r="I29" s="28"/>
       <x:c r="J29" s="53"/>
-      <x:c r="K29" s="3"/>
+      <x:c r="K29" s="66"/>
     </x:row>
     <x:row r="30" spans="1:11" ht="18" customHeight="1">
       <x:c r="A30" s="20"/>
@@ -6358,7 +6521,7 @@
       <x:c r="H30" s="54"/>
       <x:c r="I30" s="29"/>
       <x:c r="J30" s="55"/>
-      <x:c r="K30" s="3"/>
+      <x:c r="K30" s="75"/>
     </x:row>
     <x:row r="31" spans="1:11" ht="18" customHeight="1">
       <x:c r="A31" s="17"/>
@@ -6371,7 +6534,7 @@
       <x:c r="H31" s="52"/>
       <x:c r="I31" s="28"/>
       <x:c r="J31" s="53"/>
-      <x:c r="K31" s="3"/>
+      <x:c r="K31" s="66"/>
     </x:row>
     <x:row r="32" spans="1:11" ht="18" customHeight="1">
       <x:c r="A32" s="20"/>
@@ -6384,7 +6547,7 @@
       <x:c r="H32" s="54"/>
       <x:c r="I32" s="29"/>
       <x:c r="J32" s="55"/>
-      <x:c r="K32" s="3"/>
+      <x:c r="K32" s="75"/>
     </x:row>
     <x:row r="33" spans="1:11" ht="18" customHeight="1">
       <x:c r="A33" s="17"/>
@@ -6397,7 +6560,7 @@
       <x:c r="H33" s="52"/>
       <x:c r="I33" s="28"/>
       <x:c r="J33" s="53"/>
-      <x:c r="K33" s="3"/>
+      <x:c r="K33" s="66"/>
     </x:row>
     <x:row r="34" spans="1:11" ht="18" customHeight="1">
       <x:c r="A34" s="20"/>
@@ -6410,7 +6573,7 @@
       <x:c r="H34" s="54"/>
       <x:c r="I34" s="29"/>
       <x:c r="J34" s="55"/>
-      <x:c r="K34" s="3"/>
+      <x:c r="K34" s="75"/>
     </x:row>
     <x:row r="35" spans="1:11" ht="18" customHeight="1">
       <x:c r="A35" s="17"/>
@@ -6423,7 +6586,7 @@
       <x:c r="H35" s="52"/>
       <x:c r="I35" s="28"/>
       <x:c r="J35" s="53"/>
-      <x:c r="K35" s="3"/>
+      <x:c r="K35" s="66"/>
     </x:row>
     <x:row r="36" spans="1:11" ht="18" customHeight="1">
       <x:c r="A36" s="20"/>
@@ -6436,7 +6599,7 @@
       <x:c r="H36" s="54"/>
       <x:c r="I36" s="29"/>
       <x:c r="J36" s="55"/>
-      <x:c r="K36" s="3"/>
+      <x:c r="K36" s="75"/>
     </x:row>
     <x:row r="37" spans="1:11" ht="18" customHeight="1">
       <x:c r="A37" s="17"/>
@@ -6449,7 +6612,7 @@
       <x:c r="H37" s="52"/>
       <x:c r="I37" s="28"/>
       <x:c r="J37" s="53"/>
-      <x:c r="K37" s="3"/>
+      <x:c r="K37" s="66"/>
     </x:row>
     <x:row r="38" spans="1:11" ht="18" customHeight="1">
       <x:c r="A38" s="20"/>
@@ -6462,7 +6625,7 @@
       <x:c r="H38" s="54"/>
       <x:c r="I38" s="29"/>
       <x:c r="J38" s="55"/>
-      <x:c r="K38" s="3"/>
+      <x:c r="K38" s="75"/>
     </x:row>
     <x:row r="39" spans="1:11" ht="18" customHeight="1">
       <x:c r="A39" s="17"/>
@@ -6475,7 +6638,7 @@
       <x:c r="H39" s="52"/>
       <x:c r="I39" s="28"/>
       <x:c r="J39" s="53"/>
-      <x:c r="K39" s="3"/>
+      <x:c r="K39" s="66"/>
     </x:row>
     <x:row r="40" spans="1:11" ht="18" customHeight="1">
       <x:c r="A40" s="20"/>
@@ -6488,7 +6651,7 @@
       <x:c r="H40" s="54"/>
       <x:c r="I40" s="29"/>
       <x:c r="J40" s="55"/>
-      <x:c r="K40" s="3"/>
+      <x:c r="K40" s="75"/>
     </x:row>
     <x:row r="41" spans="1:11" ht="18" customHeight="1">
       <x:c r="A41" s="17"/>
@@ -6501,7 +6664,7 @@
       <x:c r="H41" s="52"/>
       <x:c r="I41" s="28"/>
       <x:c r="J41" s="53"/>
-      <x:c r="K41" s="3"/>
+      <x:c r="K41" s="66"/>
     </x:row>
     <x:row r="42" spans="1:11" ht="18" customHeight="1">
       <x:c r="A42" s="20"/>
@@ -6514,7 +6677,7 @@
       <x:c r="H42" s="54"/>
       <x:c r="I42" s="29"/>
       <x:c r="J42" s="55"/>
-      <x:c r="K42" s="3"/>
+      <x:c r="K42" s="75"/>
     </x:row>
     <x:row r="43" spans="1:11" ht="18" customHeight="1">
       <x:c r="A43" s="17"/>
@@ -6527,7 +6690,7 @@
       <x:c r="H43" s="52"/>
       <x:c r="I43" s="28"/>
       <x:c r="J43" s="53"/>
-      <x:c r="K43" s="3"/>
+      <x:c r="K43" s="66"/>
     </x:row>
     <x:row r="44" spans="1:11" ht="18" customHeight="1">
       <x:c r="A44" s="20"/>
@@ -6540,7 +6703,7 @@
       <x:c r="H44" s="54"/>
       <x:c r="I44" s="29"/>
       <x:c r="J44" s="55"/>
-      <x:c r="K44" s="3"/>
+      <x:c r="K44" s="75"/>
     </x:row>
     <x:row r="45" spans="1:11" ht="18" customHeight="1">
       <x:c r="A45" s="17"/>
@@ -6553,7 +6716,7 @@
       <x:c r="H45" s="52"/>
       <x:c r="I45" s="28"/>
       <x:c r="J45" s="53"/>
-      <x:c r="K45" s="3"/>
+      <x:c r="K45" s="66"/>
     </x:row>
     <x:row r="46" spans="1:11" ht="18" customHeight="1">
       <x:c r="A46" s="20"/>
@@ -6566,7 +6729,7 @@
       <x:c r="H46" s="54"/>
       <x:c r="I46" s="29"/>
       <x:c r="J46" s="55"/>
-      <x:c r="K46" s="3"/>
+      <x:c r="K46" s="75"/>
     </x:row>
     <x:row r="47" spans="1:11" ht="18" customHeight="1">
       <x:c r="A47" s="17"/>
@@ -6579,7 +6742,7 @@
       <x:c r="H47" s="52"/>
       <x:c r="I47" s="28"/>
       <x:c r="J47" s="53"/>
-      <x:c r="K47" s="3"/>
+      <x:c r="K47" s="66"/>
     </x:row>
     <x:row r="48" spans="1:11" ht="18" customHeight="1">
       <x:c r="A48" s="20"/>
@@ -6592,7 +6755,7 @@
       <x:c r="H48" s="54"/>
       <x:c r="I48" s="29"/>
       <x:c r="J48" s="55"/>
-      <x:c r="K48" s="3"/>
+      <x:c r="K48" s="75"/>
     </x:row>
     <x:row r="49" spans="1:11" ht="18" customHeight="1">
       <x:c r="A49" s="17"/>
@@ -6605,7 +6768,7 @@
       <x:c r="H49" s="52"/>
       <x:c r="I49" s="28"/>
       <x:c r="J49" s="53"/>
-      <x:c r="K49" s="3"/>
+      <x:c r="K49" s="66"/>
     </x:row>
     <x:row r="50" spans="1:11" ht="18" customHeight="1">
       <x:c r="A50" s="20"/>
@@ -6618,7 +6781,7 @@
       <x:c r="H50" s="54"/>
       <x:c r="I50" s="29"/>
       <x:c r="J50" s="55"/>
-      <x:c r="K50" s="3"/>
+      <x:c r="K50" s="75"/>
     </x:row>
     <x:row r="51" spans="1:11" ht="18" customHeight="1">
       <x:c r="A51" s="17"/>
@@ -6631,7 +6794,7 @@
       <x:c r="H51" s="52"/>
       <x:c r="I51" s="28"/>
       <x:c r="J51" s="53"/>
-      <x:c r="K51" s="3"/>
+      <x:c r="K51" s="66"/>
     </x:row>
     <x:row r="52" spans="1:11" ht="18" customHeight="1">
       <x:c r="A52" s="20"/>
@@ -6644,7 +6807,7 @@
       <x:c r="H52" s="54"/>
       <x:c r="I52" s="29"/>
       <x:c r="J52" s="55"/>
-      <x:c r="K52" s="3"/>
+      <x:c r="K52" s="75"/>
     </x:row>
     <x:row r="53" spans="1:11" ht="18" customHeight="1">
       <x:c r="A53" s="17"/>
@@ -6657,7 +6820,7 @@
       <x:c r="H53" s="52"/>
       <x:c r="I53" s="28"/>
       <x:c r="J53" s="53"/>
-      <x:c r="K53" s="3"/>
+      <x:c r="K53" s="66"/>
     </x:row>
     <x:row r="54" spans="1:11" ht="18" customHeight="1">
       <x:c r="A54" s="20"/>
@@ -6670,7 +6833,7 @@
       <x:c r="H54" s="54"/>
       <x:c r="I54" s="29"/>
       <x:c r="J54" s="55"/>
-      <x:c r="K54" s="3"/>
+      <x:c r="K54" s="75"/>
     </x:row>
     <x:row r="55" spans="1:11" ht="18" customHeight="1">
       <x:c r="A55" s="17"/>
@@ -6683,7 +6846,7 @@
       <x:c r="H55" s="52"/>
       <x:c r="I55" s="28"/>
       <x:c r="J55" s="53"/>
-      <x:c r="K55" s="3"/>
+      <x:c r="K55" s="66"/>
     </x:row>
     <x:row r="56" spans="1:11" ht="18" customHeight="1">
       <x:c r="A56" s="20"/>
@@ -6696,7 +6859,7 @@
       <x:c r="H56" s="54"/>
       <x:c r="I56" s="29"/>
       <x:c r="J56" s="55"/>
-      <x:c r="K56" s="3"/>
+      <x:c r="K56" s="75"/>
     </x:row>
     <x:row r="57" spans="1:11" ht="18" customHeight="1">
       <x:c r="A57" s="17"/>
@@ -6709,7 +6872,7 @@
       <x:c r="H57" s="52"/>
       <x:c r="I57" s="28"/>
       <x:c r="J57" s="53"/>
-      <x:c r="K57" s="3"/>
+      <x:c r="K57" s="66"/>
     </x:row>
     <x:row r="58" spans="1:11" ht="18" customHeight="1">
       <x:c r="A58" s="20"/>
@@ -6722,7 +6885,7 @@
       <x:c r="H58" s="54"/>
       <x:c r="I58" s="29"/>
       <x:c r="J58" s="55"/>
-      <x:c r="K58" s="3"/>
+      <x:c r="K58" s="75"/>
     </x:row>
     <x:row r="59" spans="1:11" ht="18" customHeight="1">
       <x:c r="A59" s="17"/>
@@ -6735,7 +6898,7 @@
       <x:c r="H59" s="52"/>
       <x:c r="I59" s="28"/>
       <x:c r="J59" s="53"/>
-      <x:c r="K59" s="3"/>
+      <x:c r="K59" s="66"/>
     </x:row>
     <x:row r="60" spans="1:11" ht="18" customHeight="1">
       <x:c r="A60" s="20"/>
@@ -6748,7 +6911,7 @@
       <x:c r="H60" s="54"/>
       <x:c r="I60" s="29"/>
       <x:c r="J60" s="55"/>
-      <x:c r="K60" s="3"/>
+      <x:c r="K60" s="75"/>
     </x:row>
     <x:row r="61" spans="1:11" ht="18" customHeight="1">
       <x:c r="A61" s="17"/>
@@ -6761,7 +6924,7 @@
       <x:c r="H61" s="52"/>
       <x:c r="I61" s="28"/>
       <x:c r="J61" s="53"/>
-      <x:c r="K61" s="3"/>
+      <x:c r="K61" s="66"/>
     </x:row>
     <x:row r="62" spans="1:11" ht="18" customHeight="1">
       <x:c r="A62" s="20"/>
@@ -6774,7 +6937,7 @@
       <x:c r="H62" s="54"/>
       <x:c r="I62" s="29"/>
       <x:c r="J62" s="55"/>
-      <x:c r="K62" s="3"/>
+      <x:c r="K62" s="75"/>
     </x:row>
     <x:row r="63" spans="1:11" ht="18" customHeight="1">
       <x:c r="A63" s="17"/>
@@ -6787,7 +6950,7 @@
       <x:c r="H63" s="52"/>
       <x:c r="I63" s="28"/>
       <x:c r="J63" s="53"/>
-      <x:c r="K63" s="3"/>
+      <x:c r="K63" s="66"/>
     </x:row>
     <x:row r="64" spans="1:11" ht="18" customHeight="1">
       <x:c r="A64" s="20"/>
@@ -6800,7 +6963,7 @@
       <x:c r="H64" s="54"/>
       <x:c r="I64" s="29"/>
       <x:c r="J64" s="55"/>
-      <x:c r="K64" s="3"/>
+      <x:c r="K64" s="75"/>
     </x:row>
     <x:row r="65" spans="1:11" ht="18" customHeight="1">
       <x:c r="A65" s="17"/>
@@ -6813,7 +6976,7 @@
       <x:c r="H65" s="52"/>
       <x:c r="I65" s="28"/>
       <x:c r="J65" s="53"/>
-      <x:c r="K65" s="3"/>
+      <x:c r="K65" s="66"/>
     </x:row>
     <x:row r="66" spans="1:11" ht="18" customHeight="1">
       <x:c r="A66" s="20"/>
@@ -6826,7 +6989,7 @@
       <x:c r="H66" s="54"/>
       <x:c r="I66" s="29"/>
       <x:c r="J66" s="55"/>
-      <x:c r="K66" s="3"/>
+      <x:c r="K66" s="75"/>
     </x:row>
     <x:row r="67" spans="1:11" ht="18" customHeight="1">
       <x:c r="A67" s="17"/>
@@ -6839,7 +7002,7 @@
       <x:c r="H67" s="52"/>
       <x:c r="I67" s="28"/>
       <x:c r="J67" s="53"/>
-      <x:c r="K67" s="3"/>
+      <x:c r="K67" s="66"/>
     </x:row>
     <x:row r="68" spans="1:11" ht="18" customHeight="1">
       <x:c r="A68" s="20"/>
@@ -6852,7 +7015,7 @@
       <x:c r="H68" s="54"/>
       <x:c r="I68" s="29"/>
       <x:c r="J68" s="55"/>
-      <x:c r="K68" s="3"/>
+      <x:c r="K68" s="75"/>
     </x:row>
     <x:row r="69" spans="1:11" ht="18" customHeight="1">
       <x:c r="A69" s="17"/>
@@ -6865,7 +7028,7 @@
       <x:c r="H69" s="52"/>
       <x:c r="I69" s="28"/>
       <x:c r="J69" s="53"/>
-      <x:c r="K69" s="3"/>
+      <x:c r="K69" s="66"/>
     </x:row>
     <x:row r="70" spans="1:11" ht="18" customHeight="1">
       <x:c r="A70" s="20"/>
@@ -6878,7 +7041,7 @@
       <x:c r="H70" s="54"/>
       <x:c r="I70" s="29"/>
       <x:c r="J70" s="55"/>
-      <x:c r="K70" s="3"/>
+      <x:c r="K70" s="75"/>
     </x:row>
     <x:row r="71" spans="1:11" ht="18" customHeight="1">
       <x:c r="A71" s="17"/>
@@ -6891,7 +7054,7 @@
       <x:c r="H71" s="52"/>
       <x:c r="I71" s="28"/>
       <x:c r="J71" s="53"/>
-      <x:c r="K71" s="3"/>
+      <x:c r="K71" s="66"/>
     </x:row>
     <x:row r="72" spans="1:11" ht="18" customHeight="1">
       <x:c r="A72" s="20"/>
@@ -6904,7 +7067,7 @@
       <x:c r="H72" s="54"/>
       <x:c r="I72" s="29"/>
       <x:c r="J72" s="55"/>
-      <x:c r="K72" s="3"/>
+      <x:c r="K72" s="75"/>
     </x:row>
     <x:row r="73" spans="1:11" ht="18" customHeight="1">
       <x:c r="A73" s="17"/>
@@ -6917,7 +7080,7 @@
       <x:c r="H73" s="52"/>
       <x:c r="I73" s="28"/>
       <x:c r="J73" s="53"/>
-      <x:c r="K73" s="3"/>
+      <x:c r="K73" s="66"/>
     </x:row>
     <x:row r="74" spans="1:11" ht="18" customHeight="1">
       <x:c r="A74" s="20"/>
@@ -6930,7 +7093,7 @@
       <x:c r="H74" s="54"/>
       <x:c r="I74" s="29"/>
       <x:c r="J74" s="55"/>
-      <x:c r="K74" s="3"/>
+      <x:c r="K74" s="75"/>
     </x:row>
     <x:row r="75" spans="1:11" ht="18" customHeight="1">
       <x:c r="A75" s="17"/>
@@ -6943,7 +7106,7 @@
       <x:c r="H75" s="52"/>
       <x:c r="I75" s="28"/>
       <x:c r="J75" s="53"/>
-      <x:c r="K75" s="3"/>
+      <x:c r="K75" s="66"/>
     </x:row>
     <x:row r="76" spans="1:11" ht="18" customHeight="1">
       <x:c r="A76" s="20"/>
@@ -6956,7 +7119,7 @@
       <x:c r="H76" s="54"/>
       <x:c r="I76" s="29"/>
       <x:c r="J76" s="55"/>
-      <x:c r="K76" s="3"/>
+      <x:c r="K76" s="75"/>
     </x:row>
     <x:row r="77" spans="1:11" ht="18" customHeight="1">
       <x:c r="A77" s="17"/>
@@ -6969,7 +7132,7 @@
       <x:c r="H77" s="52"/>
       <x:c r="I77" s="28"/>
       <x:c r="J77" s="53"/>
-      <x:c r="K77" s="3"/>
+      <x:c r="K77" s="66"/>
     </x:row>
     <x:row r="78" spans="1:11" ht="18" customHeight="1">
       <x:c r="A78" s="20"/>
@@ -6982,7 +7145,7 @@
       <x:c r="H78" s="54"/>
       <x:c r="I78" s="29"/>
       <x:c r="J78" s="55"/>
-      <x:c r="K78" s="3"/>
+      <x:c r="K78" s="75"/>
     </x:row>
     <x:row r="79" spans="1:11" ht="18" customHeight="1">
       <x:c r="A79" s="17"/>
@@ -6995,7 +7158,7 @@
       <x:c r="H79" s="52"/>
       <x:c r="I79" s="28"/>
       <x:c r="J79" s="53"/>
-      <x:c r="K79" s="3"/>
+      <x:c r="K79" s="66"/>
     </x:row>
     <x:row r="80" spans="1:11" ht="18" customHeight="1">
       <x:c r="A80" s="20"/>
@@ -7008,7 +7171,7 @@
       <x:c r="H80" s="54"/>
       <x:c r="I80" s="29"/>
       <x:c r="J80" s="55"/>
-      <x:c r="K80" s="3"/>
+      <x:c r="K80" s="75"/>
     </x:row>
     <x:row r="81" spans="1:11" ht="18" customHeight="1">
       <x:c r="A81" s="17"/>
@@ -7021,7 +7184,7 @@
       <x:c r="H81" s="52"/>
       <x:c r="I81" s="28"/>
       <x:c r="J81" s="53"/>
-      <x:c r="K81" s="3"/>
+      <x:c r="K81" s="66"/>
     </x:row>
     <x:row r="82" spans="1:11" ht="18" customHeight="1">
       <x:c r="A82" s="20"/>
@@ -7034,7 +7197,7 @@
       <x:c r="H82" s="54"/>
       <x:c r="I82" s="29"/>
       <x:c r="J82" s="55"/>
-      <x:c r="K82" s="3"/>
+      <x:c r="K82" s="75"/>
     </x:row>
     <x:row r="83" spans="1:11" ht="18" customHeight="1">
       <x:c r="A83" s="17"/>
@@ -7047,7 +7210,7 @@
       <x:c r="H83" s="52"/>
       <x:c r="I83" s="28"/>
       <x:c r="J83" s="53"/>
-      <x:c r="K83" s="3"/>
+      <x:c r="K83" s="66"/>
     </x:row>
     <x:row r="84" spans="1:11" ht="18" customHeight="1">
       <x:c r="A84" s="20"/>
@@ -7060,7 +7223,7 @@
       <x:c r="H84" s="54"/>
       <x:c r="I84" s="29"/>
       <x:c r="J84" s="55"/>
-      <x:c r="K84" s="3"/>
+      <x:c r="K84" s="75"/>
     </x:row>
     <x:row r="85" spans="1:11" ht="18" customHeight="1">
       <x:c r="A85" s="17"/>
@@ -7073,7 +7236,7 @@
       <x:c r="H85" s="52"/>
       <x:c r="I85" s="28"/>
       <x:c r="J85" s="53"/>
-      <x:c r="K85" s="3"/>
+      <x:c r="K85" s="66"/>
     </x:row>
     <x:row r="86" spans="1:11" ht="18" customHeight="1">
       <x:c r="A86" s="20"/>
@@ -7086,7 +7249,7 @@
       <x:c r="H86" s="54"/>
       <x:c r="I86" s="29"/>
       <x:c r="J86" s="55"/>
-      <x:c r="K86" s="3"/>
+      <x:c r="K86" s="75"/>
     </x:row>
     <x:row r="87" spans="1:11" ht="18" customHeight="1">
       <x:c r="A87" s="17"/>
@@ -7099,7 +7262,7 @@
       <x:c r="H87" s="52"/>
       <x:c r="I87" s="28"/>
       <x:c r="J87" s="53"/>
-      <x:c r="K87" s="3"/>
+      <x:c r="K87" s="66"/>
     </x:row>
     <x:row r="88" spans="1:11" ht="18" customHeight="1">
       <x:c r="A88" s="20"/>
@@ -7112,7 +7275,7 @@
       <x:c r="H88" s="54"/>
       <x:c r="I88" s="29"/>
       <x:c r="J88" s="55"/>
-      <x:c r="K88" s="3"/>
+      <x:c r="K88" s="75"/>
     </x:row>
     <x:row r="89" spans="1:11" ht="18" customHeight="1">
       <x:c r="A89" s="17"/>
@@ -7125,7 +7288,7 @@
       <x:c r="H89" s="52"/>
       <x:c r="I89" s="28"/>
       <x:c r="J89" s="53"/>
-      <x:c r="K89" s="3"/>
+      <x:c r="K89" s="66"/>
     </x:row>
     <x:row r="90" spans="1:11" ht="18" customHeight="1">
       <x:c r="A90" s="20"/>
@@ -7138,7 +7301,7 @@
       <x:c r="H90" s="54"/>
       <x:c r="I90" s="29"/>
       <x:c r="J90" s="55"/>
-      <x:c r="K90" s="3"/>
+      <x:c r="K90" s="75"/>
     </x:row>
     <x:row r="91" spans="1:11" ht="18" customHeight="1">
       <x:c r="A91" s="17"/>
@@ -7151,7 +7314,7 @@
       <x:c r="H91" s="52"/>
       <x:c r="I91" s="28"/>
       <x:c r="J91" s="53"/>
-      <x:c r="K91" s="3"/>
+      <x:c r="K91" s="66"/>
     </x:row>
     <x:row r="92" spans="1:11" ht="18" customHeight="1">
       <x:c r="A92" s="20"/>
@@ -7164,7 +7327,7 @@
       <x:c r="H92" s="54"/>
       <x:c r="I92" s="29"/>
       <x:c r="J92" s="55"/>
-      <x:c r="K92" s="3"/>
+      <x:c r="K92" s="75"/>
     </x:row>
     <x:row r="93" spans="1:11" ht="18" customHeight="1">
       <x:c r="A93" s="17"/>
@@ -7177,7 +7340,7 @@
       <x:c r="H93" s="52"/>
       <x:c r="I93" s="28"/>
       <x:c r="J93" s="53"/>
-      <x:c r="K93" s="3"/>
+      <x:c r="K93" s="66"/>
     </x:row>
     <x:row r="94" spans="1:11" ht="18" customHeight="1">
       <x:c r="A94" s="20"/>
@@ -7190,7 +7353,7 @@
       <x:c r="H94" s="54"/>
       <x:c r="I94" s="29"/>
       <x:c r="J94" s="55"/>
-      <x:c r="K94" s="3"/>
+      <x:c r="K94" s="75"/>
     </x:row>
     <x:row r="95" spans="1:11" ht="18" customHeight="1">
       <x:c r="A95" s="17"/>
@@ -7203,7 +7366,7 @@
       <x:c r="H95" s="52"/>
       <x:c r="I95" s="28"/>
       <x:c r="J95" s="53"/>
-      <x:c r="K95" s="3"/>
+      <x:c r="K95" s="66"/>
     </x:row>
     <x:row r="96" spans="1:11" ht="18" customHeight="1">
       <x:c r="A96" s="20"/>
@@ -7216,7 +7379,7 @@
       <x:c r="H96" s="54"/>
       <x:c r="I96" s="29"/>
       <x:c r="J96" s="55"/>
-      <x:c r="K96" s="3"/>
+      <x:c r="K96" s="75"/>
     </x:row>
     <x:row r="97" spans="1:11" ht="18" customHeight="1">
       <x:c r="A97" s="17"/>
@@ -7229,7 +7392,7 @@
       <x:c r="H97" s="52"/>
       <x:c r="I97" s="28"/>
       <x:c r="J97" s="53"/>
-      <x:c r="K97" s="3"/>
+      <x:c r="K97" s="66"/>
     </x:row>
     <x:row r="98" spans="1:11" ht="18" customHeight="1">
       <x:c r="A98" s="20"/>
@@ -7242,7 +7405,7 @@
       <x:c r="H98" s="54"/>
       <x:c r="I98" s="29"/>
       <x:c r="J98" s="55"/>
-      <x:c r="K98" s="3"/>
+      <x:c r="K98" s="75"/>
     </x:row>
     <x:row r="99" spans="1:11" ht="18" customHeight="1">
       <x:c r="A99" s="17"/>
@@ -7255,7 +7418,7 @@
       <x:c r="H99" s="52"/>
       <x:c r="I99" s="28"/>
       <x:c r="J99" s="53"/>
-      <x:c r="K99" s="3"/>
+      <x:c r="K99" s="66"/>
     </x:row>
     <x:row r="100" spans="1:11" ht="18" customHeight="1">
       <x:c r="A100" s="20"/>
@@ -7268,7 +7431,7 @@
       <x:c r="H100" s="54"/>
       <x:c r="I100" s="29"/>
       <x:c r="J100" s="55"/>
-      <x:c r="K100" s="3"/>
+      <x:c r="K100" s="75"/>
     </x:row>
     <x:row r="101" spans="1:11" ht="18" customHeight="1">
       <x:c r="A101" s="17"/>
@@ -7281,7 +7444,7 @@
       <x:c r="H101" s="52"/>
       <x:c r="I101" s="28"/>
       <x:c r="J101" s="53"/>
-      <x:c r="K101" s="3"/>
+      <x:c r="K101" s="66"/>
     </x:row>
     <x:row r="102" spans="1:11" ht="18" customHeight="1">
       <x:c r="A102" s="20"/>
@@ -7294,7 +7457,7 @@
       <x:c r="H102" s="54"/>
       <x:c r="I102" s="29"/>
       <x:c r="J102" s="55"/>
-      <x:c r="K102" s="3"/>
+      <x:c r="K102" s="75"/>
     </x:row>
     <x:row r="103" spans="1:11" ht="18" customHeight="1">
       <x:c r="A103" s="17"/>
@@ -7307,7 +7470,7 @@
       <x:c r="H103" s="52"/>
       <x:c r="I103" s="28"/>
       <x:c r="J103" s="53"/>
-      <x:c r="K103" s="3"/>
+      <x:c r="K103" s="66"/>
     </x:row>
     <x:row r="104" spans="1:11" ht="18" customHeight="1">
       <x:c r="A104" s="20"/>
@@ -7320,7 +7483,7 @@
       <x:c r="H104" s="54"/>
       <x:c r="I104" s="29"/>
       <x:c r="J104" s="55"/>
-      <x:c r="K104" s="3"/>
+      <x:c r="K104" s="75"/>
     </x:row>
     <x:row r="105" spans="1:11" ht="18" customHeight="1">
       <x:c r="A105" s="17"/>
@@ -7333,7 +7496,7 @@
       <x:c r="H105" s="52"/>
       <x:c r="I105" s="28"/>
       <x:c r="J105" s="53"/>
-      <x:c r="K105" s="3"/>
+      <x:c r="K105" s="66"/>
     </x:row>
     <x:row r="106" spans="1:11" ht="18" customHeight="1">
       <x:c r="A106" s="20"/>
@@ -7346,7 +7509,7 @@
       <x:c r="H106" s="54"/>
       <x:c r="I106" s="29"/>
       <x:c r="J106" s="55"/>
-      <x:c r="K106" s="3"/>
+      <x:c r="K106" s="75"/>
     </x:row>
     <x:row r="107" spans="1:11" ht="18" customHeight="1">
       <x:c r="A107" s="17"/>
@@ -7359,7 +7522,7 @@
       <x:c r="H107" s="52"/>
       <x:c r="I107" s="28"/>
       <x:c r="J107" s="53"/>
-      <x:c r="K107" s="3"/>
+      <x:c r="K107" s="66"/>
     </x:row>
     <x:row r="108" spans="1:11" ht="18" customHeight="1">
       <x:c r="A108" s="20"/>
@@ -7372,7 +7535,7 @@
       <x:c r="H108" s="54"/>
       <x:c r="I108" s="29"/>
       <x:c r="J108" s="55"/>
-      <x:c r="K108" s="3"/>
+      <x:c r="K108" s="75"/>
     </x:row>
     <x:row r="109" spans="1:11" ht="18" customHeight="1">
       <x:c r="A109" s="17"/>
@@ -7385,7 +7548,7 @@
       <x:c r="H109" s="52"/>
       <x:c r="I109" s="28"/>
       <x:c r="J109" s="53"/>
-      <x:c r="K109" s="3"/>
+      <x:c r="K109" s="66"/>
     </x:row>
     <x:row r="110" spans="1:11" ht="18" customHeight="1">
       <x:c r="A110" s="20"/>
@@ -7398,7 +7561,7 @@
       <x:c r="H110" s="54"/>
       <x:c r="I110" s="29"/>
       <x:c r="J110" s="55"/>
-      <x:c r="K110" s="3"/>
+      <x:c r="K110" s="75"/>
     </x:row>
     <x:row r="111" spans="1:11" ht="18" customHeight="1">
       <x:c r="A111" s="17"/>
@@ -7411,7 +7574,7 @@
       <x:c r="H111" s="52"/>
       <x:c r="I111" s="28"/>
       <x:c r="J111" s="53"/>
-      <x:c r="K111" s="3"/>
+      <x:c r="K111" s="66"/>
     </x:row>
     <x:row r="112" spans="1:11" ht="18" customHeight="1">
       <x:c r="A112" s="20"/>
@@ -7424,7 +7587,7 @@
       <x:c r="H112" s="54"/>
       <x:c r="I112" s="29"/>
       <x:c r="J112" s="55"/>
-      <x:c r="K112" s="3"/>
+      <x:c r="K112" s="75"/>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="3"/>
@@ -7531,20 +7694,12 @@
       <x:c r="K120" s="3"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="A5:J5"/>
-    <x:mergeCell ref="A3:J3"/>
-    <x:mergeCell ref="B1:G1"/>
-    <x:mergeCell ref="A4:J4"/>
-    <x:mergeCell ref="A2:J2"/>
-    <x:mergeCell ref="I1:J1"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet7">
     <x:tabColor rgb="ff7fdd55"/>
@@ -7560,151 +7715,158 @@
     <x:col min="7" max="8" width="16" style="2" customWidth="1"/>
     <x:col min="9" max="9" width="12" style="2" customWidth="1"/>
     <x:col min="10" max="10" width="20" style="2" customWidth="1"/>
+    <x:col min="11" max="11" width="10" style="2" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="96" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B1" s="135"/>
-      <x:c r="C1" s="132"/>
-      <x:c r="D1" s="132"/>
-      <x:c r="E1" s="132"/>
-      <x:c r="F1" s="132"/>
-      <x:c r="G1" s="133"/>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B1" s="133"/>
+      <x:c r="C1" s="130"/>
+      <x:c r="D1" s="130"/>
+      <x:c r="E1" s="130"/>
+      <x:c r="F1" s="130"/>
+      <x:c r="G1" s="131"/>
       <x:c r="H1" s="96" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="I1" s="136"/>
-      <x:c r="J1" s="133"/>
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="I1" s="134"/>
+      <x:c r="J1" s="131"/>
       <x:c r="K1" s="3"/>
     </x:row>
     <x:row r="2" spans="1:11" ht="16" customHeight="1">
-      <x:c r="A2" s="134" t="s">
+      <x:c r="A2" s="132" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B2" s="134"/>
-      <x:c r="C2" s="134"/>
-      <x:c r="D2" s="134"/>
-      <x:c r="E2" s="134"/>
-      <x:c r="F2" s="134"/>
-      <x:c r="G2" s="134"/>
-      <x:c r="H2" s="134"/>
-      <x:c r="I2" s="134"/>
-      <x:c r="J2" s="134"/>
+      <x:c r="B2" s="132"/>
+      <x:c r="C2" s="132"/>
+      <x:c r="D2" s="132"/>
+      <x:c r="E2" s="132"/>
+      <x:c r="F2" s="132"/>
+      <x:c r="G2" s="132"/>
+      <x:c r="H2" s="132"/>
+      <x:c r="I2" s="132"/>
+      <x:c r="J2" s="132"/>
       <x:c r="K2" s="3"/>
     </x:row>
     <x:row r="3" spans="1:11" ht="16" customHeight="1">
-      <x:c r="A3" s="134" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B3" s="134"/>
-      <x:c r="C3" s="134"/>
-      <x:c r="D3" s="134"/>
-      <x:c r="E3" s="134"/>
-      <x:c r="F3" s="134"/>
-      <x:c r="G3" s="134"/>
-      <x:c r="H3" s="134"/>
-      <x:c r="I3" s="134"/>
-      <x:c r="J3" s="134"/>
+      <x:c r="A3" s="132" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B3" s="132"/>
+      <x:c r="C3" s="132"/>
+      <x:c r="D3" s="132"/>
+      <x:c r="E3" s="132"/>
+      <x:c r="F3" s="132"/>
+      <x:c r="G3" s="132"/>
+      <x:c r="H3" s="132"/>
+      <x:c r="I3" s="132"/>
+      <x:c r="J3" s="132"/>
       <x:c r="K3" s="3"/>
     </x:row>
     <x:row r="4" spans="1:11" ht="16" customHeight="1">
-      <x:c r="A4" s="134" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B4" s="134"/>
-      <x:c r="C4" s="134"/>
-      <x:c r="D4" s="134"/>
-      <x:c r="E4" s="134"/>
-      <x:c r="F4" s="134"/>
-      <x:c r="G4" s="134"/>
-      <x:c r="H4" s="134"/>
-      <x:c r="I4" s="134"/>
-      <x:c r="J4" s="134"/>
+      <x:c r="A4" s="132" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="132"/>
+      <x:c r="C4" s="132"/>
+      <x:c r="D4" s="132"/>
+      <x:c r="E4" s="132"/>
+      <x:c r="F4" s="132"/>
+      <x:c r="G4" s="132"/>
+      <x:c r="H4" s="132"/>
+      <x:c r="I4" s="132"/>
+      <x:c r="J4" s="132"/>
       <x:c r="K4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:11">
-      <x:c r="A5" s="131" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B5" s="132"/>
-      <x:c r="C5" s="132"/>
-      <x:c r="D5" s="132"/>
-      <x:c r="E5" s="132"/>
-      <x:c r="F5" s="132"/>
-      <x:c r="G5" s="132"/>
-      <x:c r="H5" s="132"/>
-      <x:c r="I5" s="132"/>
-      <x:c r="J5" s="133"/>
+      <x:c r="A5" s="129" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B5" s="130"/>
+      <x:c r="C5" s="130"/>
+      <x:c r="D5" s="130"/>
+      <x:c r="E5" s="130"/>
+      <x:c r="F5" s="130"/>
+      <x:c r="G5" s="130"/>
+      <x:c r="H5" s="130"/>
+      <x:c r="I5" s="130"/>
+      <x:c r="J5" s="131"/>
       <x:c r="K5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="97" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B6" s="98" t="s">
-        <x:v>100</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C6" s="99" t="s">
-        <x:v>88</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D6" s="100" t="s">
-        <x:v>93</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E6" s="101" t="s">
-        <x:v>84</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F6" s="101" t="s">
-        <x:v>85</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G6" s="102" t="s">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H6" s="102" t="s">
-        <x:v>43</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I6" s="103" t="s">
-        <x:v>142</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="J6" s="104" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="K6" s="3"/>
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="K6" s="104" t="s">
+        <x:v>178</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="105" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B7" s="106" t="s">
-        <x:v>172</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C7" s="107" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D7" s="108" t="s">
-        <x:v>66</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E7" s="114"/>
       <x:c r="F7" s="115"/>
       <x:c r="G7" s="118"/>
       <x:c r="H7" s="118"/>
       <x:c r="I7" s="122"/>
-      <x:c r="J7" s="119"/>
-      <x:c r="K7" s="3"/>
+      <x:c r="J7" s="7" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="K7" s="119" t="s">
+        <x:v>136</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="109" t="s">
-        <x:v>132</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B8" s="110" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C8" s="116" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D8" s="111" t="s">
-        <x:v>1</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E8" s="112"/>
       <x:c r="F8" s="113"/>
@@ -7712,43 +7874,43 @@
       <x:c r="H8" s="120"/>
       <x:c r="I8" s="117"/>
       <x:c r="J8" s="121"/>
-      <x:c r="K8" s="3"/>
+      <x:c r="K8" s="121"/>
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="105" t="s">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B9" s="106" t="s">
-        <x:v>137</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C9" s="107"/>
       <x:c r="D9" s="108" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E9" s="114" t="s">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F9" s="115" t="s">
-        <x:v>170</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G9" s="118"/>
       <x:c r="H9" s="118"/>
       <x:c r="I9" s="122"/>
       <x:c r="J9" s="119"/>
-      <x:c r="K9" s="3"/>
+      <x:c r="K9" s="119"/>
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="109" t="s">
-        <x:v>170</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B10" s="110" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C10" s="116" t="s">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D10" s="111" t="s">
-        <x:v>123</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E10" s="112"/>
       <x:c r="F10" s="113"/>
@@ -7756,20 +7918,20 @@
       <x:c r="H10" s="120"/>
       <x:c r="I10" s="117"/>
       <x:c r="J10" s="121"/>
-      <x:c r="K10" s="3"/>
+      <x:c r="K10" s="121"/>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="105" t="s">
-        <x:v>171</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B11" s="106" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C11" s="107" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D11" s="108" t="s">
-        <x:v>114</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E11" s="114"/>
       <x:c r="F11" s="115"/>
@@ -7777,43 +7939,43 @@
       <x:c r="H11" s="118"/>
       <x:c r="I11" s="122"/>
       <x:c r="J11" s="119"/>
-      <x:c r="K11" s="3"/>
+      <x:c r="K11" s="119"/>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="109" t="s">
-        <x:v>165</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B12" s="110" t="s">
-        <x:v>137</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C12" s="116"/>
       <x:c r="D12" s="111" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E12" s="112" t="s">
-        <x:v>153</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="F12" s="113" t="s">
-        <x:v>167</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G12" s="120"/>
       <x:c r="H12" s="120"/>
       <x:c r="I12" s="117"/>
       <x:c r="J12" s="121"/>
-      <x:c r="K12" s="3"/>
+      <x:c r="K12" s="121"/>
     </x:row>
     <x:row r="13" spans="1:11" ht="18" customHeight="1">
       <x:c r="A13" s="17" t="s">
-        <x:v>167</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B13" s="86" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C13" s="87" t="s">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D13" s="88" t="s">
-        <x:v>241</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="E13" s="89"/>
       <x:c r="F13" s="90"/>
@@ -7821,41 +7983,43 @@
       <x:c r="H13" s="52"/>
       <x:c r="I13" s="28"/>
       <x:c r="J13" s="53"/>
-      <x:c r="K13" s="3"/>
+      <x:c r="K13" s="119"/>
     </x:row>
     <x:row r="14" spans="1:11" ht="18" customHeight="1">
       <x:c r="A14" s="20" t="s">
-        <x:v>164</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B14" s="91" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C14" s="92" t="s">
-        <x:v>132</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D14" s="93" t="s">
-        <x:v>187</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E14" s="94"/>
       <x:c r="F14" s="95"/>
       <x:c r="G14" s="54"/>
       <x:c r="H14" s="54"/>
       <x:c r="I14" s="29"/>
-      <x:c r="J14" s="55"/>
-      <x:c r="K14" s="3"/>
+      <x:c r="J14" s="7" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K14" s="121"/>
     </x:row>
     <x:row r="15" spans="1:11" ht="18" customHeight="1">
       <x:c r="A15" s="17" t="s">
-        <x:v>162</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B15" s="86" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C15" s="87" t="s">
-        <x:v>155</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D15" s="88" t="s">
-        <x:v>186</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="E15" s="89"/>
       <x:c r="F15" s="90"/>
@@ -7863,20 +8027,20 @@
       <x:c r="H15" s="52"/>
       <x:c r="I15" s="28"/>
       <x:c r="J15" s="53"/>
-      <x:c r="K15" s="3"/>
+      <x:c r="K15" s="119"/>
     </x:row>
     <x:row r="16" spans="1:11" ht="18" customHeight="1">
       <x:c r="A16" s="20" t="s">
-        <x:v>163</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B16" s="91" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C16" s="92" t="s">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D16" s="93" t="s">
-        <x:v>182</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E16" s="94"/>
       <x:c r="F16" s="95"/>
@@ -7884,7 +8048,7 @@
       <x:c r="H16" s="54"/>
       <x:c r="I16" s="29"/>
       <x:c r="J16" s="55"/>
-      <x:c r="K16" s="3"/>
+      <x:c r="K16" s="121"/>
     </x:row>
     <x:row r="17" spans="1:11" ht="18" customHeight="1">
       <x:c r="A17" s="17"/>
@@ -7897,7 +8061,7 @@
       <x:c r="H17" s="52"/>
       <x:c r="I17" s="28"/>
       <x:c r="J17" s="53"/>
-      <x:c r="K17" s="3"/>
+      <x:c r="K17" s="119"/>
     </x:row>
     <x:row r="18" spans="1:11" ht="18" customHeight="1">
       <x:c r="A18" s="20"/>
@@ -7910,7 +8074,7 @@
       <x:c r="H18" s="54"/>
       <x:c r="I18" s="29"/>
       <x:c r="J18" s="55"/>
-      <x:c r="K18" s="3"/>
+      <x:c r="K18" s="121"/>
     </x:row>
     <x:row r="19" spans="1:11" ht="18" customHeight="1">
       <x:c r="A19" s="17"/>
@@ -7923,7 +8087,7 @@
       <x:c r="H19" s="52"/>
       <x:c r="I19" s="28"/>
       <x:c r="J19" s="53"/>
-      <x:c r="K19" s="3"/>
+      <x:c r="K19" s="119"/>
     </x:row>
     <x:row r="20" spans="1:11" ht="18" customHeight="1">
       <x:c r="A20" s="20"/>
@@ -7936,7 +8100,7 @@
       <x:c r="H20" s="54"/>
       <x:c r="I20" s="29"/>
       <x:c r="J20" s="55"/>
-      <x:c r="K20" s="3"/>
+      <x:c r="K20" s="121"/>
     </x:row>
     <x:row r="21" spans="1:11" ht="18" customHeight="1">
       <x:c r="A21" s="17"/>
@@ -7949,7 +8113,7 @@
       <x:c r="H21" s="52"/>
       <x:c r="I21" s="28"/>
       <x:c r="J21" s="53"/>
-      <x:c r="K21" s="3"/>
+      <x:c r="K21" s="119"/>
     </x:row>
     <x:row r="22" spans="1:11" ht="18" customHeight="1">
       <x:c r="A22" s="20"/>
@@ -7962,7 +8126,7 @@
       <x:c r="H22" s="54"/>
       <x:c r="I22" s="29"/>
       <x:c r="J22" s="55"/>
-      <x:c r="K22" s="3"/>
+      <x:c r="K22" s="121"/>
     </x:row>
     <x:row r="23" spans="1:11" ht="18" customHeight="1">
       <x:c r="A23" s="17"/>
@@ -7975,7 +8139,7 @@
       <x:c r="H23" s="52"/>
       <x:c r="I23" s="28"/>
       <x:c r="J23" s="53"/>
-      <x:c r="K23" s="3"/>
+      <x:c r="K23" s="119"/>
     </x:row>
     <x:row r="24" spans="1:11" ht="18" customHeight="1">
       <x:c r="A24" s="20"/>
@@ -7988,7 +8152,7 @@
       <x:c r="H24" s="54"/>
       <x:c r="I24" s="29"/>
       <x:c r="J24" s="55"/>
-      <x:c r="K24" s="3"/>
+      <x:c r="K24" s="121"/>
     </x:row>
     <x:row r="25" spans="1:11" ht="18" customHeight="1">
       <x:c r="A25" s="17"/>
@@ -8001,7 +8165,7 @@
       <x:c r="H25" s="52"/>
       <x:c r="I25" s="28"/>
       <x:c r="J25" s="53"/>
-      <x:c r="K25" s="3"/>
+      <x:c r="K25" s="119"/>
     </x:row>
     <x:row r="26" spans="1:11" ht="18" customHeight="1">
       <x:c r="A26" s="20"/>
@@ -8014,7 +8178,7 @@
       <x:c r="H26" s="54"/>
       <x:c r="I26" s="29"/>
       <x:c r="J26" s="55"/>
-      <x:c r="K26" s="3"/>
+      <x:c r="K26" s="121"/>
     </x:row>
     <x:row r="27" spans="1:11" ht="18" customHeight="1">
       <x:c r="A27" s="17"/>
@@ -8027,7 +8191,7 @@
       <x:c r="H27" s="52"/>
       <x:c r="I27" s="28"/>
       <x:c r="J27" s="53"/>
-      <x:c r="K27" s="3"/>
+      <x:c r="K27" s="119"/>
     </x:row>
     <x:row r="28" spans="1:11" ht="18" customHeight="1">
       <x:c r="A28" s="20"/>
@@ -8040,7 +8204,7 @@
       <x:c r="H28" s="54"/>
       <x:c r="I28" s="29"/>
       <x:c r="J28" s="55"/>
-      <x:c r="K28" s="3"/>
+      <x:c r="K28" s="121"/>
     </x:row>
     <x:row r="29" spans="1:11" ht="18" customHeight="1">
       <x:c r="A29" s="17"/>
@@ -8053,7 +8217,7 @@
       <x:c r="H29" s="52"/>
       <x:c r="I29" s="28"/>
       <x:c r="J29" s="53"/>
-      <x:c r="K29" s="3"/>
+      <x:c r="K29" s="119"/>
     </x:row>
     <x:row r="30" spans="1:11" ht="18" customHeight="1">
       <x:c r="A30" s="20"/>
@@ -8066,7 +8230,7 @@
       <x:c r="H30" s="54"/>
       <x:c r="I30" s="29"/>
       <x:c r="J30" s="55"/>
-      <x:c r="K30" s="3"/>
+      <x:c r="K30" s="121"/>
     </x:row>
     <x:row r="31" spans="1:11" ht="18" customHeight="1">
       <x:c r="A31" s="17"/>
@@ -8079,7 +8243,7 @@
       <x:c r="H31" s="52"/>
       <x:c r="I31" s="28"/>
       <x:c r="J31" s="53"/>
-      <x:c r="K31" s="3"/>
+      <x:c r="K31" s="119"/>
     </x:row>
     <x:row r="32" spans="1:11" ht="18" customHeight="1">
       <x:c r="A32" s="20"/>
@@ -8092,7 +8256,7 @@
       <x:c r="H32" s="54"/>
       <x:c r="I32" s="29"/>
       <x:c r="J32" s="55"/>
-      <x:c r="K32" s="3"/>
+      <x:c r="K32" s="121"/>
     </x:row>
     <x:row r="33" spans="1:11" ht="18" customHeight="1">
       <x:c r="A33" s="17"/>
@@ -8105,7 +8269,7 @@
       <x:c r="H33" s="52"/>
       <x:c r="I33" s="28"/>
       <x:c r="J33" s="53"/>
-      <x:c r="K33" s="3"/>
+      <x:c r="K33" s="119"/>
     </x:row>
     <x:row r="34" spans="1:11" ht="18" customHeight="1">
       <x:c r="A34" s="20"/>
@@ -8118,7 +8282,7 @@
       <x:c r="H34" s="54"/>
       <x:c r="I34" s="29"/>
       <x:c r="J34" s="55"/>
-      <x:c r="K34" s="3"/>
+      <x:c r="K34" s="121"/>
     </x:row>
     <x:row r="35" spans="1:11" ht="18" customHeight="1">
       <x:c r="A35" s="17"/>
@@ -8131,7 +8295,7 @@
       <x:c r="H35" s="52"/>
       <x:c r="I35" s="28"/>
       <x:c r="J35" s="53"/>
-      <x:c r="K35" s="3"/>
+      <x:c r="K35" s="119"/>
     </x:row>
     <x:row r="36" spans="1:11" ht="18" customHeight="1">
       <x:c r="A36" s="20"/>
@@ -8144,7 +8308,7 @@
       <x:c r="H36" s="54"/>
       <x:c r="I36" s="29"/>
       <x:c r="J36" s="55"/>
-      <x:c r="K36" s="3"/>
+      <x:c r="K36" s="121"/>
     </x:row>
     <x:row r="37" spans="1:11" ht="18" customHeight="1">
       <x:c r="A37" s="17"/>
@@ -8157,7 +8321,7 @@
       <x:c r="H37" s="52"/>
       <x:c r="I37" s="28"/>
       <x:c r="J37" s="53"/>
-      <x:c r="K37" s="3"/>
+      <x:c r="K37" s="119"/>
     </x:row>
     <x:row r="38" spans="1:11" ht="18" customHeight="1">
       <x:c r="A38" s="20"/>
@@ -8170,7 +8334,7 @@
       <x:c r="H38" s="54"/>
       <x:c r="I38" s="29"/>
       <x:c r="J38" s="55"/>
-      <x:c r="K38" s="3"/>
+      <x:c r="K38" s="121"/>
     </x:row>
     <x:row r="39" spans="1:11" ht="18" customHeight="1">
       <x:c r="A39" s="17"/>
@@ -8183,7 +8347,7 @@
       <x:c r="H39" s="52"/>
       <x:c r="I39" s="28"/>
       <x:c r="J39" s="53"/>
-      <x:c r="K39" s="3"/>
+      <x:c r="K39" s="119"/>
     </x:row>
     <x:row r="40" spans="1:11" ht="18" customHeight="1">
       <x:c r="A40" s="20"/>
@@ -8196,7 +8360,7 @@
       <x:c r="H40" s="54"/>
       <x:c r="I40" s="29"/>
       <x:c r="J40" s="55"/>
-      <x:c r="K40" s="3"/>
+      <x:c r="K40" s="121"/>
     </x:row>
     <x:row r="41" spans="1:11" ht="18" customHeight="1">
       <x:c r="A41" s="17"/>
@@ -8209,7 +8373,7 @@
       <x:c r="H41" s="52"/>
       <x:c r="I41" s="28"/>
       <x:c r="J41" s="53"/>
-      <x:c r="K41" s="3"/>
+      <x:c r="K41" s="119"/>
     </x:row>
     <x:row r="42" spans="1:11" ht="18" customHeight="1">
       <x:c r="A42" s="20"/>
@@ -8222,7 +8386,7 @@
       <x:c r="H42" s="54"/>
       <x:c r="I42" s="29"/>
       <x:c r="J42" s="55"/>
-      <x:c r="K42" s="3"/>
+      <x:c r="K42" s="121"/>
     </x:row>
     <x:row r="43" spans="1:11" ht="18" customHeight="1">
       <x:c r="A43" s="17"/>
@@ -8235,7 +8399,7 @@
       <x:c r="H43" s="52"/>
       <x:c r="I43" s="28"/>
       <x:c r="J43" s="53"/>
-      <x:c r="K43" s="3"/>
+      <x:c r="K43" s="119"/>
     </x:row>
     <x:row r="44" spans="1:11" ht="18" customHeight="1">
       <x:c r="A44" s="20"/>
@@ -8248,7 +8412,7 @@
       <x:c r="H44" s="54"/>
       <x:c r="I44" s="29"/>
       <x:c r="J44" s="55"/>
-      <x:c r="K44" s="3"/>
+      <x:c r="K44" s="121"/>
     </x:row>
     <x:row r="45" spans="1:11" ht="18" customHeight="1">
       <x:c r="A45" s="17"/>
@@ -8261,7 +8425,7 @@
       <x:c r="H45" s="52"/>
       <x:c r="I45" s="28"/>
       <x:c r="J45" s="53"/>
-      <x:c r="K45" s="3"/>
+      <x:c r="K45" s="119"/>
     </x:row>
     <x:row r="46" spans="1:11" ht="18" customHeight="1">
       <x:c r="A46" s="20"/>
@@ -8274,7 +8438,7 @@
       <x:c r="H46" s="54"/>
       <x:c r="I46" s="29"/>
       <x:c r="J46" s="55"/>
-      <x:c r="K46" s="3"/>
+      <x:c r="K46" s="121"/>
     </x:row>
     <x:row r="47" spans="1:11" ht="18" customHeight="1">
       <x:c r="A47" s="17"/>
@@ -8287,7 +8451,7 @@
       <x:c r="H47" s="52"/>
       <x:c r="I47" s="28"/>
       <x:c r="J47" s="53"/>
-      <x:c r="K47" s="3"/>
+      <x:c r="K47" s="119"/>
     </x:row>
     <x:row r="48" spans="1:11" ht="18" customHeight="1">
       <x:c r="A48" s="20"/>
@@ -8300,7 +8464,7 @@
       <x:c r="H48" s="54"/>
       <x:c r="I48" s="29"/>
       <x:c r="J48" s="55"/>
-      <x:c r="K48" s="3"/>
+      <x:c r="K48" s="121"/>
     </x:row>
     <x:row r="49" spans="1:11" ht="18" customHeight="1">
       <x:c r="A49" s="17"/>
@@ -8313,7 +8477,7 @@
       <x:c r="H49" s="52"/>
       <x:c r="I49" s="28"/>
       <x:c r="J49" s="53"/>
-      <x:c r="K49" s="3"/>
+      <x:c r="K49" s="119"/>
     </x:row>
     <x:row r="50" spans="1:11" ht="18" customHeight="1">
       <x:c r="A50" s="20"/>
@@ -8326,7 +8490,7 @@
       <x:c r="H50" s="54"/>
       <x:c r="I50" s="29"/>
       <x:c r="J50" s="55"/>
-      <x:c r="K50" s="3"/>
+      <x:c r="K50" s="121"/>
     </x:row>
     <x:row r="51" spans="1:11" ht="18" customHeight="1">
       <x:c r="A51" s="17"/>
@@ -8339,7 +8503,7 @@
       <x:c r="H51" s="52"/>
       <x:c r="I51" s="28"/>
       <x:c r="J51" s="53"/>
-      <x:c r="K51" s="3"/>
+      <x:c r="K51" s="119"/>
     </x:row>
     <x:row r="52" spans="1:11" ht="18" customHeight="1">
       <x:c r="A52" s="20"/>
@@ -8352,7 +8516,7 @@
       <x:c r="H52" s="54"/>
       <x:c r="I52" s="29"/>
       <x:c r="J52" s="55"/>
-      <x:c r="K52" s="3"/>
+      <x:c r="K52" s="121"/>
     </x:row>
     <x:row r="53" spans="1:11" ht="18" customHeight="1">
       <x:c r="A53" s="17"/>
@@ -8365,7 +8529,7 @@
       <x:c r="H53" s="52"/>
       <x:c r="I53" s="28"/>
       <x:c r="J53" s="53"/>
-      <x:c r="K53" s="3"/>
+      <x:c r="K53" s="119"/>
     </x:row>
     <x:row r="54" spans="1:11" ht="18" customHeight="1">
       <x:c r="A54" s="20"/>
@@ -8378,7 +8542,7 @@
       <x:c r="H54" s="54"/>
       <x:c r="I54" s="29"/>
       <x:c r="J54" s="55"/>
-      <x:c r="K54" s="3"/>
+      <x:c r="K54" s="121"/>
     </x:row>
     <x:row r="55" spans="1:11" ht="18" customHeight="1">
       <x:c r="A55" s="17"/>
@@ -8391,7 +8555,7 @@
       <x:c r="H55" s="52"/>
       <x:c r="I55" s="28"/>
       <x:c r="J55" s="53"/>
-      <x:c r="K55" s="3"/>
+      <x:c r="K55" s="119"/>
     </x:row>
     <x:row r="56" spans="1:11" ht="18" customHeight="1">
       <x:c r="A56" s="20"/>
@@ -8404,7 +8568,7 @@
       <x:c r="H56" s="54"/>
       <x:c r="I56" s="29"/>
       <x:c r="J56" s="55"/>
-      <x:c r="K56" s="3"/>
+      <x:c r="K56" s="121"/>
     </x:row>
     <x:row r="57" spans="1:11" ht="18" customHeight="1">
       <x:c r="A57" s="17"/>
@@ -8417,7 +8581,7 @@
       <x:c r="H57" s="52"/>
       <x:c r="I57" s="28"/>
       <x:c r="J57" s="53"/>
-      <x:c r="K57" s="3"/>
+      <x:c r="K57" s="119"/>
     </x:row>
     <x:row r="58" spans="1:11" ht="18" customHeight="1">
       <x:c r="A58" s="20"/>
@@ -8430,7 +8594,7 @@
       <x:c r="H58" s="54"/>
       <x:c r="I58" s="29"/>
       <x:c r="J58" s="55"/>
-      <x:c r="K58" s="3"/>
+      <x:c r="K58" s="121"/>
     </x:row>
     <x:row r="59" spans="1:11" ht="18" customHeight="1">
       <x:c r="A59" s="17"/>
@@ -8443,7 +8607,7 @@
       <x:c r="H59" s="52"/>
       <x:c r="I59" s="28"/>
       <x:c r="J59" s="53"/>
-      <x:c r="K59" s="3"/>
+      <x:c r="K59" s="119"/>
     </x:row>
     <x:row r="60" spans="1:11" ht="18" customHeight="1">
       <x:c r="A60" s="20"/>
@@ -8456,7 +8620,7 @@
       <x:c r="H60" s="54"/>
       <x:c r="I60" s="29"/>
       <x:c r="J60" s="55"/>
-      <x:c r="K60" s="3"/>
+      <x:c r="K60" s="121"/>
     </x:row>
     <x:row r="61" spans="1:11" ht="18" customHeight="1">
       <x:c r="A61" s="17"/>
@@ -8469,7 +8633,7 @@
       <x:c r="H61" s="52"/>
       <x:c r="I61" s="28"/>
       <x:c r="J61" s="53"/>
-      <x:c r="K61" s="3"/>
+      <x:c r="K61" s="119"/>
     </x:row>
     <x:row r="62" spans="1:11" ht="18" customHeight="1">
       <x:c r="A62" s="20"/>
@@ -8482,7 +8646,7 @@
       <x:c r="H62" s="54"/>
       <x:c r="I62" s="29"/>
       <x:c r="J62" s="55"/>
-      <x:c r="K62" s="3"/>
+      <x:c r="K62" s="121"/>
     </x:row>
     <x:row r="63" spans="1:11" ht="18" customHeight="1">
       <x:c r="A63" s="17"/>
@@ -8495,7 +8659,7 @@
       <x:c r="H63" s="52"/>
       <x:c r="I63" s="28"/>
       <x:c r="J63" s="53"/>
-      <x:c r="K63" s="3"/>
+      <x:c r="K63" s="119"/>
     </x:row>
     <x:row r="64" spans="1:11" ht="18" customHeight="1">
       <x:c r="A64" s="20"/>
@@ -8508,7 +8672,7 @@
       <x:c r="H64" s="54"/>
       <x:c r="I64" s="29"/>
       <x:c r="J64" s="55"/>
-      <x:c r="K64" s="3"/>
+      <x:c r="K64" s="121"/>
     </x:row>
     <x:row r="65" spans="1:11" ht="18" customHeight="1">
       <x:c r="A65" s="17"/>
@@ -8521,7 +8685,7 @@
       <x:c r="H65" s="52"/>
       <x:c r="I65" s="28"/>
       <x:c r="J65" s="53"/>
-      <x:c r="K65" s="3"/>
+      <x:c r="K65" s="119"/>
     </x:row>
     <x:row r="66" spans="1:11" ht="18" customHeight="1">
       <x:c r="A66" s="20"/>
@@ -8534,7 +8698,7 @@
       <x:c r="H66" s="54"/>
       <x:c r="I66" s="29"/>
       <x:c r="J66" s="55"/>
-      <x:c r="K66" s="3"/>
+      <x:c r="K66" s="121"/>
     </x:row>
     <x:row r="67" spans="1:11" ht="18" customHeight="1">
       <x:c r="A67" s="17"/>
@@ -8547,7 +8711,7 @@
       <x:c r="H67" s="52"/>
       <x:c r="I67" s="28"/>
       <x:c r="J67" s="53"/>
-      <x:c r="K67" s="3"/>
+      <x:c r="K67" s="119"/>
     </x:row>
     <x:row r="68" spans="1:11" ht="18" customHeight="1">
       <x:c r="A68" s="20"/>
@@ -8560,7 +8724,7 @@
       <x:c r="H68" s="54"/>
       <x:c r="I68" s="29"/>
       <x:c r="J68" s="55"/>
-      <x:c r="K68" s="3"/>
+      <x:c r="K68" s="121"/>
     </x:row>
     <x:row r="69" spans="1:11" ht="18" customHeight="1">
       <x:c r="A69" s="17"/>
@@ -8573,7 +8737,7 @@
       <x:c r="H69" s="52"/>
       <x:c r="I69" s="28"/>
       <x:c r="J69" s="53"/>
-      <x:c r="K69" s="3"/>
+      <x:c r="K69" s="119"/>
     </x:row>
     <x:row r="70" spans="1:11" ht="18" customHeight="1">
       <x:c r="A70" s="20"/>
@@ -8586,7 +8750,7 @@
       <x:c r="H70" s="54"/>
       <x:c r="I70" s="29"/>
       <x:c r="J70" s="55"/>
-      <x:c r="K70" s="3"/>
+      <x:c r="K70" s="121"/>
     </x:row>
     <x:row r="71" spans="1:11" ht="18" customHeight="1">
       <x:c r="A71" s="17"/>
@@ -8599,7 +8763,7 @@
       <x:c r="H71" s="52"/>
       <x:c r="I71" s="28"/>
       <x:c r="J71" s="53"/>
-      <x:c r="K71" s="3"/>
+      <x:c r="K71" s="119"/>
     </x:row>
     <x:row r="72" spans="1:11" ht="18" customHeight="1">
       <x:c r="A72" s="20"/>
@@ -8612,7 +8776,7 @@
       <x:c r="H72" s="54"/>
       <x:c r="I72" s="29"/>
       <x:c r="J72" s="55"/>
-      <x:c r="K72" s="3"/>
+      <x:c r="K72" s="121"/>
     </x:row>
     <x:row r="73" spans="1:11" ht="18" customHeight="1">
       <x:c r="A73" s="17"/>
@@ -8625,7 +8789,7 @@
       <x:c r="H73" s="52"/>
       <x:c r="I73" s="28"/>
       <x:c r="J73" s="53"/>
-      <x:c r="K73" s="3"/>
+      <x:c r="K73" s="119"/>
     </x:row>
     <x:row r="74" spans="1:11" ht="18" customHeight="1">
       <x:c r="A74" s="20"/>
@@ -8638,7 +8802,7 @@
       <x:c r="H74" s="54"/>
       <x:c r="I74" s="29"/>
       <x:c r="J74" s="55"/>
-      <x:c r="K74" s="3"/>
+      <x:c r="K74" s="121"/>
     </x:row>
     <x:row r="75" spans="1:11" ht="18" customHeight="1">
       <x:c r="A75" s="17"/>
@@ -8651,7 +8815,7 @@
       <x:c r="H75" s="52"/>
       <x:c r="I75" s="28"/>
       <x:c r="J75" s="53"/>
-      <x:c r="K75" s="3"/>
+      <x:c r="K75" s="119"/>
     </x:row>
     <x:row r="76" spans="1:11" ht="18" customHeight="1">
       <x:c r="A76" s="20"/>
@@ -8664,7 +8828,7 @@
       <x:c r="H76" s="54"/>
       <x:c r="I76" s="29"/>
       <x:c r="J76" s="55"/>
-      <x:c r="K76" s="3"/>
+      <x:c r="K76" s="121"/>
     </x:row>
     <x:row r="77" spans="1:11" ht="18" customHeight="1">
       <x:c r="A77" s="17"/>
@@ -8677,7 +8841,7 @@
       <x:c r="H77" s="52"/>
       <x:c r="I77" s="28"/>
       <x:c r="J77" s="53"/>
-      <x:c r="K77" s="3"/>
+      <x:c r="K77" s="119"/>
     </x:row>
     <x:row r="78" spans="1:11" ht="18" customHeight="1">
       <x:c r="A78" s="20"/>
@@ -8690,7 +8854,7 @@
       <x:c r="H78" s="54"/>
       <x:c r="I78" s="29"/>
       <x:c r="J78" s="55"/>
-      <x:c r="K78" s="3"/>
+      <x:c r="K78" s="121"/>
     </x:row>
     <x:row r="79" spans="1:11" ht="18" customHeight="1">
       <x:c r="A79" s="17"/>
@@ -8703,7 +8867,7 @@
       <x:c r="H79" s="52"/>
       <x:c r="I79" s="28"/>
       <x:c r="J79" s="53"/>
-      <x:c r="K79" s="3"/>
+      <x:c r="K79" s="119"/>
     </x:row>
     <x:row r="80" spans="1:11" ht="18" customHeight="1">
       <x:c r="A80" s="20"/>
@@ -8716,7 +8880,7 @@
       <x:c r="H80" s="54"/>
       <x:c r="I80" s="29"/>
       <x:c r="J80" s="55"/>
-      <x:c r="K80" s="3"/>
+      <x:c r="K80" s="121"/>
     </x:row>
     <x:row r="81" spans="1:11" ht="18" customHeight="1">
       <x:c r="A81" s="17"/>
@@ -8729,7 +8893,7 @@
       <x:c r="H81" s="52"/>
       <x:c r="I81" s="28"/>
       <x:c r="J81" s="53"/>
-      <x:c r="K81" s="3"/>
+      <x:c r="K81" s="119"/>
     </x:row>
     <x:row r="82" spans="1:11" ht="18" customHeight="1">
       <x:c r="A82" s="20"/>
@@ -8742,7 +8906,7 @@
       <x:c r="H82" s="54"/>
       <x:c r="I82" s="29"/>
       <x:c r="J82" s="55"/>
-      <x:c r="K82" s="3"/>
+      <x:c r="K82" s="121"/>
     </x:row>
     <x:row r="83" spans="1:11" ht="18" customHeight="1">
       <x:c r="A83" s="17"/>
@@ -8755,7 +8919,7 @@
       <x:c r="H83" s="52"/>
       <x:c r="I83" s="28"/>
       <x:c r="J83" s="53"/>
-      <x:c r="K83" s="3"/>
+      <x:c r="K83" s="119"/>
     </x:row>
     <x:row r="84" spans="1:11" ht="18" customHeight="1">
       <x:c r="A84" s="20"/>
@@ -8768,7 +8932,7 @@
       <x:c r="H84" s="54"/>
       <x:c r="I84" s="29"/>
       <x:c r="J84" s="55"/>
-      <x:c r="K84" s="3"/>
+      <x:c r="K84" s="121"/>
     </x:row>
     <x:row r="85" spans="1:11" ht="18" customHeight="1">
       <x:c r="A85" s="17"/>
@@ -8781,7 +8945,7 @@
       <x:c r="H85" s="52"/>
       <x:c r="I85" s="28"/>
       <x:c r="J85" s="53"/>
-      <x:c r="K85" s="3"/>
+      <x:c r="K85" s="119"/>
     </x:row>
     <x:row r="86" spans="1:11" ht="18" customHeight="1">
       <x:c r="A86" s="20"/>
@@ -8794,7 +8958,7 @@
       <x:c r="H86" s="54"/>
       <x:c r="I86" s="29"/>
       <x:c r="J86" s="55"/>
-      <x:c r="K86" s="3"/>
+      <x:c r="K86" s="121"/>
     </x:row>
     <x:row r="87" spans="1:11" ht="18" customHeight="1">
       <x:c r="A87" s="17"/>
@@ -8807,7 +8971,7 @@
       <x:c r="H87" s="52"/>
       <x:c r="I87" s="28"/>
       <x:c r="J87" s="53"/>
-      <x:c r="K87" s="3"/>
+      <x:c r="K87" s="119"/>
     </x:row>
     <x:row r="88" spans="1:11" ht="18" customHeight="1">
       <x:c r="A88" s="20"/>
@@ -8820,7 +8984,7 @@
       <x:c r="H88" s="54"/>
       <x:c r="I88" s="29"/>
       <x:c r="J88" s="55"/>
-      <x:c r="K88" s="3"/>
+      <x:c r="K88" s="121"/>
     </x:row>
     <x:row r="89" spans="1:11" ht="18" customHeight="1">
       <x:c r="A89" s="17"/>
@@ -8833,7 +8997,7 @@
       <x:c r="H89" s="52"/>
       <x:c r="I89" s="28"/>
       <x:c r="J89" s="53"/>
-      <x:c r="K89" s="3"/>
+      <x:c r="K89" s="119"/>
     </x:row>
     <x:row r="90" spans="1:11" ht="18" customHeight="1">
       <x:c r="A90" s="20"/>
@@ -8846,7 +9010,7 @@
       <x:c r="H90" s="54"/>
       <x:c r="I90" s="29"/>
       <x:c r="J90" s="55"/>
-      <x:c r="K90" s="3"/>
+      <x:c r="K90" s="121"/>
     </x:row>
     <x:row r="91" spans="1:11" ht="18" customHeight="1">
       <x:c r="A91" s="17"/>
@@ -8859,7 +9023,7 @@
       <x:c r="H91" s="52"/>
       <x:c r="I91" s="28"/>
       <x:c r="J91" s="53"/>
-      <x:c r="K91" s="3"/>
+      <x:c r="K91" s="119"/>
     </x:row>
     <x:row r="92" spans="1:11" ht="18" customHeight="1">
       <x:c r="A92" s="20"/>
@@ -8872,7 +9036,7 @@
       <x:c r="H92" s="54"/>
       <x:c r="I92" s="29"/>
       <x:c r="J92" s="55"/>
-      <x:c r="K92" s="3"/>
+      <x:c r="K92" s="121"/>
     </x:row>
     <x:row r="93" spans="1:11" ht="18" customHeight="1">
       <x:c r="A93" s="17"/>
@@ -8885,7 +9049,7 @@
       <x:c r="H93" s="52"/>
       <x:c r="I93" s="28"/>
       <x:c r="J93" s="53"/>
-      <x:c r="K93" s="3"/>
+      <x:c r="K93" s="119"/>
     </x:row>
     <x:row r="94" spans="1:11" ht="18" customHeight="1">
       <x:c r="A94" s="20"/>
@@ -8898,7 +9062,7 @@
       <x:c r="H94" s="54"/>
       <x:c r="I94" s="29"/>
       <x:c r="J94" s="55"/>
-      <x:c r="K94" s="3"/>
+      <x:c r="K94" s="121"/>
     </x:row>
     <x:row r="95" spans="1:11" ht="18" customHeight="1">
       <x:c r="A95" s="17"/>
@@ -8911,7 +9075,7 @@
       <x:c r="H95" s="52"/>
       <x:c r="I95" s="28"/>
       <x:c r="J95" s="53"/>
-      <x:c r="K95" s="3"/>
+      <x:c r="K95" s="119"/>
     </x:row>
     <x:row r="96" spans="1:11" ht="18" customHeight="1">
       <x:c r="A96" s="20"/>
@@ -8924,7 +9088,7 @@
       <x:c r="H96" s="54"/>
       <x:c r="I96" s="29"/>
       <x:c r="J96" s="55"/>
-      <x:c r="K96" s="3"/>
+      <x:c r="K96" s="121"/>
     </x:row>
     <x:row r="97" spans="1:11" ht="18" customHeight="1">
       <x:c r="A97" s="17"/>
@@ -8937,7 +9101,7 @@
       <x:c r="H97" s="52"/>
       <x:c r="I97" s="28"/>
       <x:c r="J97" s="53"/>
-      <x:c r="K97" s="3"/>
+      <x:c r="K97" s="119"/>
     </x:row>
     <x:row r="98" spans="1:11" ht="18" customHeight="1">
       <x:c r="A98" s="20"/>
@@ -8950,7 +9114,7 @@
       <x:c r="H98" s="54"/>
       <x:c r="I98" s="29"/>
       <x:c r="J98" s="55"/>
-      <x:c r="K98" s="3"/>
+      <x:c r="K98" s="121"/>
     </x:row>
     <x:row r="99" spans="1:11" ht="18" customHeight="1">
       <x:c r="A99" s="17"/>
@@ -8963,7 +9127,7 @@
       <x:c r="H99" s="52"/>
       <x:c r="I99" s="28"/>
       <x:c r="J99" s="53"/>
-      <x:c r="K99" s="3"/>
+      <x:c r="K99" s="119"/>
     </x:row>
     <x:row r="100" spans="1:11" ht="18" customHeight="1">
       <x:c r="A100" s="20"/>
@@ -8976,7 +9140,7 @@
       <x:c r="H100" s="54"/>
       <x:c r="I100" s="29"/>
       <x:c r="J100" s="55"/>
-      <x:c r="K100" s="3"/>
+      <x:c r="K100" s="121"/>
     </x:row>
     <x:row r="101" spans="1:11" ht="18" customHeight="1">
       <x:c r="A101" s="17"/>
@@ -8989,7 +9153,7 @@
       <x:c r="H101" s="52"/>
       <x:c r="I101" s="28"/>
       <x:c r="J101" s="53"/>
-      <x:c r="K101" s="3"/>
+      <x:c r="K101" s="119"/>
     </x:row>
     <x:row r="102" spans="1:11" ht="18" customHeight="1">
       <x:c r="A102" s="20"/>
@@ -9002,7 +9166,7 @@
       <x:c r="H102" s="54"/>
       <x:c r="I102" s="29"/>
       <x:c r="J102" s="55"/>
-      <x:c r="K102" s="3"/>
+      <x:c r="K102" s="121"/>
     </x:row>
     <x:row r="103" spans="1:11" ht="18" customHeight="1">
       <x:c r="A103" s="17"/>
@@ -9015,7 +9179,7 @@
       <x:c r="H103" s="52"/>
       <x:c r="I103" s="28"/>
       <x:c r="J103" s="53"/>
-      <x:c r="K103" s="3"/>
+      <x:c r="K103" s="119"/>
     </x:row>
     <x:row r="104" spans="1:11" ht="18" customHeight="1">
       <x:c r="A104" s="20"/>
@@ -9028,7 +9192,7 @@
       <x:c r="H104" s="54"/>
       <x:c r="I104" s="29"/>
       <x:c r="J104" s="55"/>
-      <x:c r="K104" s="3"/>
+      <x:c r="K104" s="121"/>
     </x:row>
     <x:row r="105" spans="1:11" ht="18" customHeight="1">
       <x:c r="A105" s="17"/>
@@ -9041,7 +9205,7 @@
       <x:c r="H105" s="52"/>
       <x:c r="I105" s="28"/>
       <x:c r="J105" s="53"/>
-      <x:c r="K105" s="3"/>
+      <x:c r="K105" s="119"/>
     </x:row>
     <x:row r="106" spans="1:11" ht="18" customHeight="1">
       <x:c r="A106" s="20"/>
@@ -9054,7 +9218,7 @@
       <x:c r="H106" s="54"/>
       <x:c r="I106" s="29"/>
       <x:c r="J106" s="55"/>
-      <x:c r="K106" s="3"/>
+      <x:c r="K106" s="121"/>
     </x:row>
     <x:row r="107" spans="1:11" ht="18" customHeight="1">
       <x:c r="A107" s="17"/>
@@ -9067,7 +9231,7 @@
       <x:c r="H107" s="52"/>
       <x:c r="I107" s="28"/>
       <x:c r="J107" s="53"/>
-      <x:c r="K107" s="3"/>
+      <x:c r="K107" s="119"/>
     </x:row>
     <x:row r="108" spans="1:11" ht="18" customHeight="1">
       <x:c r="A108" s="20"/>
@@ -9080,7 +9244,7 @@
       <x:c r="H108" s="54"/>
       <x:c r="I108" s="29"/>
       <x:c r="J108" s="55"/>
-      <x:c r="K108" s="3"/>
+      <x:c r="K108" s="121"/>
     </x:row>
     <x:row r="109" spans="1:11" ht="18" customHeight="1">
       <x:c r="A109" s="17"/>
@@ -9093,7 +9257,7 @@
       <x:c r="H109" s="52"/>
       <x:c r="I109" s="28"/>
       <x:c r="J109" s="53"/>
-      <x:c r="K109" s="3"/>
+      <x:c r="K109" s="119"/>
     </x:row>
     <x:row r="110" spans="1:11" ht="18" customHeight="1">
       <x:c r="A110" s="20"/>
@@ -9106,7 +9270,7 @@
       <x:c r="H110" s="54"/>
       <x:c r="I110" s="29"/>
       <x:c r="J110" s="55"/>
-      <x:c r="K110" s="3"/>
+      <x:c r="K110" s="121"/>
     </x:row>
     <x:row r="111" spans="1:11" ht="18" customHeight="1">
       <x:c r="A111" s="17"/>
@@ -9119,7 +9283,7 @@
       <x:c r="H111" s="52"/>
       <x:c r="I111" s="28"/>
       <x:c r="J111" s="53"/>
-      <x:c r="K111" s="3"/>
+      <x:c r="K111" s="119"/>
     </x:row>
     <x:row r="112" spans="1:11" ht="18" customHeight="1">
       <x:c r="A112" s="20"/>
@@ -9132,7 +9296,7 @@
       <x:c r="H112" s="54"/>
       <x:c r="I112" s="29"/>
       <x:c r="J112" s="55"/>
-      <x:c r="K112" s="3"/>
+      <x:c r="K112" s="121"/>
     </x:row>
     <x:row r="113" spans="1:11">
       <x:c r="A113" s="3"/>
@@ -9239,15 +9403,7 @@
       <x:c r="K120" s="3"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="6">
-    <x:mergeCell ref="A5:J5"/>
-    <x:mergeCell ref="A3:J3"/>
-    <x:mergeCell ref="B1:G1"/>
-    <x:mergeCell ref="A4:J4"/>
-    <x:mergeCell ref="A2:J2"/>
-    <x:mergeCell ref="I1:J1"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/Games/Codes/Dialogues/NeuralRust_Dialogue.xlsx
+++ b/Games/Codes/Dialogues/NeuralRust_Dialogue.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11865" activeTab="6"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="17565" windowHeight="6735" activeTab="1"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="CAST" sheetId="1" r:id="rId4"/>
@@ -25,758 +25,755 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="257">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="255">
+  <x:si>
+    <x:t>// P : Player 고정 — 수정 불가  |  단축어는 대사 시트 char 컬럼에 입력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sprite.x-=dist; tweens: x+=dist, alpha→1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sprite.x+=dist; tweens: x-=dist, alpha→1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// fx 컬럼에 예약어 입력  |  복합(Y끼리만): shake_screen|fade_out_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 파라미터 커스텀: shake_char:intensity=5,duration=300  (기본값 사용 시 예약어만 입력)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 배경 태그 → 파일명 매핑  |  파일명은 확장자 제외, Assets/Sprites/Backgrounds/ 경로 기준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flash_screen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_shock_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fade_in_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_door_open</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그렇군요... 잘 쉬세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shake_screen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bgm_shop_theme</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카메라 줌 아웃 (원복)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 ID (시트명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 왼쪽 슬라이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>textbox_flash</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 오른쪽 슬라이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>별칭 (sfx 컬럼에 입력)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: alpha→1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>닉네임 (대화창 표시명)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_happy_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slide_out_right</x:t>
+  </x:si>
+  <x:si>
+    <x:t>speed_up_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slide_in_right</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오른쪽에서 슬라이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>── 전체 동시 (all)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>태그 (bg 컬럼에 입력)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_typing_loop</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Background_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오늘 하루는 어떠셨나요?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이핑 속도 감속 (강조)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_beep_alert</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=250</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slide_in_left</x:t>
+  </x:si>
+  <x:si>
+    <x:t>textbox_fade_in</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: alpha→0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scale_up_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>textbox_shake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 번쩍 (피격/강조)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slide_out_left</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fade_out_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상점 입장 (동일 유지 시 복사)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>textbox_fade_out</x:t>
+  </x:si>
+  <x:si>
+    <x:t>── 캐릭터 단독 (char)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천천히 배우면 될 거라 생각합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그럼 인수인계를 시작하겠습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>── 화면 전체 (screen)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이핑 일시 정지 (극적 침묵)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bgm_calm_morning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 색조 (분노/상태이상)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>── 대화창 / UI (ui)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>음. . . 뭐, 상관 없나.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scene_transition</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 별칭을 대사 시트 sfx 컬럼에 입력 — 파일명 자동 매핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: x ±intensity, yoyo, repeat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.flash(dur, r, g, b)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogManager.setTypingSpeed(speed)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아무튼, 새롭게 외각 지부 관리자로 부임하신 것을 축하드립니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: dialogBox alpha 0.2→1, yoyo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.fadeIn(dur, r, g, b)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.shake(dur, intensity)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.fadeOut(dur, r, g, b)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogManager.pauseTyping(duration)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 태그는 대사 시트 bg 컬럼에 입력  |  공백=이전 배경 유지  |  NONE=배경 제거  |  전환 접두어: instant:A  fade_black:B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flag_set</x:t>
+  </x:si>
+  <x:si>
+    <x:t>player_rude</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_confirm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>speed=0.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아, 미안해요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>slow_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>blackout</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[DIALOGUE]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발화 캐릭터만 진동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 페이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flash_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zoom_out</x:t>
+  </x:si>
+  <x:si>
+    <x:t>whiteout</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타이핑 속도 배속</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 페이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>//관리자 캐릭터.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화창 페이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>day1_1_done</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 순간 번쩍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shop_Open</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내일도 잘 부탁해요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pan_camera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 페이드 아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tint_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그걸 왜 물어?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_cancel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화창 페이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ CAST ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx_sad_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>repeat=2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>shake_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외곽 지부 - 복도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bounce_char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 강조 확대</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Phaser3 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fade_out</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 화이트아웃</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 전체 진동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전체 암전 후 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>왼쪽에서 슬라이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>flag_check</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pause_text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화면 페이드 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외곽 지부 - 외부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// sfx: SFX 탭 별칭 (복합: Happy|Beep)  |  fx: FX 탭 예약어 (복합: shake_char|fade_out, 파라미터: shake_char:intensity=5)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// BGM 없는 이벤트는 행 비워두기  |  같은 BGM 유지 시 동일 파일명 복사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: y-=height, yoyo, ease:Bounce</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.flash(dur, 255,255,255)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: dialogBox x ±intensity, yoyo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogBox.setAlpha(0); tweens: alpha→1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 닉네임: 비어있으면 캐릭터명 사용  |  ???처럼 미공개명 가능  |  런타임 변경: SaveManager.setFlag('cast_nick_A', 'Noa')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// char: CAST 탭 단축어 (P 고정)  |  expr: 001~999, 공백=이전 표정 유지  |  choice: 1=선택지 줄</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// target — screen: 카메라  |  char: 현재 발화 캐릭터  |  ui: 대화창  |  all: 전체</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 복합 사용: Happy|Door  처럼 | 로 구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: alpha 0↔1, yoyo, repeat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: scaleX/Y→scale, yoyo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fadeOut → onComplete: 다음 시트 로드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>말 그대로 외각 지부입니다, 별 볼 일 없는 곳이죠.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.fadeOut → alpha 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sprite.setTint → clearTint()</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.zoomTo(zoom, dur)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저는 외곽 지부에 이전 관리자 노아(Noa)라고 합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// goto: 같은 시트 line_id | END | 다음 시트명  |  숫자 ID도 텍스트 서식으로 처리됨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 표정: b001 → Character_[캐릭터명]_001 자동 매핑  |  expr 공백 = 이전 표정 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메모</x:t>
+  </x:si>
+  <x:si>
+    <x:t>L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>END</x:t>
+  </x:si>
+  <x:si>
+    <x:t>005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>all</x:t>
+  </x:si>
+  <x:si>
+    <x:t>009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Q</x:t>
+  </x:si>
+  <x:si>
+    <x:t>K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예약어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Noa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>노아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ui</x:t>
+  </x:si>
+  <x:si>
+    <x:t>I</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sfx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sad</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단축어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t>N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fx</x:t>
+  </x:si>
+  <x:si>
+    <x:t>O</x:t>
+  </x:si>
+  <x:si>
+    <x:t>007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M</x:t>
+  </x:si>
+  <x:si>
+    <x:t>030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>???</x:t>
+  </x:si>
+  <x:si>
+    <x:t>004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D</x:t>
+  </x:si>
+  <x:si>
+    <x:t>006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>expr</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반갑습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shock</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배경 파일명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>line_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Happy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카메라 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ BG ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>target</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화창 진동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬픈 반응</x:t>
+  </x:si>
+  <x:si>
+    <x:t>zoom_in</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Beep</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Door</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 열림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카메라 줌 인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부임이라니?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>choice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그저 그랬어.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상점 해금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ FX ]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템 알림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGM 파일명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외곽 지부?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Player</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UI 취소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>screen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shop_In</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SFX 파일명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>char</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씬 전환 연출</x:t>
+  </x:si>
   <x:si>
     <x:t>푸른 곰팡이</x:t>
   </x:si>
   <x:si>
-    <x:t>// 파라미터 커스텀: shake_char:intensity=5,duration=300  (기본값 사용 시 예약어만 입력)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 배경 태그 → 파일명 매핑  |  파일명은 확장자 제외, Assets/Sprites/Backgrounds/ 경로 기준</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// fx 컬럼에 예약어 입력  |  복합(Y끼리만): shake_screen|fade_out_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 태그는 대사 시트 bg 컬럼에 입력  |  공백=이전 배경 유지  |  NONE=배경 제거  |  전환 접두어: instant:A  fade_black:B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// sfx: SFX 탭 별칭 (복합: Happy|Beep)  |  fx: FX 탭 예약어 (복합: shake_char|fade_out, 파라미터: shake_char:intensity=5)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// BGM 없는 이벤트는 행 비워두기  |  같은 BGM 유지 시 동일 파일명 복사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// P : Player 고정 — 수정 불가  |  단축어는 대사 시트 char 컬럼에 입력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// target — screen: 카메라  |  char: 현재 발화 캐릭터  |  ui: 대화창  |  all: 전체</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// goto: 같은 시트 line_id | END | 다음 시트명  |  숫자 ID도 텍스트 서식으로 처리됨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 표정: b001 → Character_[캐릭터명]_001 자동 매핑  |  expr 공백 = 이전 표정 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// char: CAST 탭 단축어 (P 고정)  |  expr: 001~999, 공백=이전 표정 유지  |  choice: 1=선택지 줄</x:t>
-  </x:si>
-  <x:si>
-    <x:t>왼쪽에서 슬라이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 강조 확대</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 암전 후 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전체 화이트아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flash_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외곽 지부 - 외부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Phaser3 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fade_out</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외곽 지부 - 복도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 페이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bounce_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 페이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_confirm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 전체 진동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발화 캐릭터만 진동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>blackout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>pause_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이핑 속도 배속</x:t>
-  </x:si>
-  <x:si>
-    <x:t>speed=0.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 순간 번쩍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>//관리자 캐릭터.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>whiteout</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화창 페이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[DIALOGUE]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그걸 왜 물어?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flag_set</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zoom_out</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내일도 잘 부탁해요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아, 미안해요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>player_rude</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flag_check</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slow_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>pan_camera</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 페이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tint_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>day1_1_done</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shop_Open</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ CAST ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화창 페이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>shake_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>repeat=2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 닉네임: 비어있으면 캐릭터명 사용  |  ???처럼 미공개명 가능  |  런타임 변경: SaveManager.setFlag('cast_nick_A', 'Noa')</x:t>
-  </x:si>
-  <x:si>
-    <x:t>음. . . 뭐, 상관 없나.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>textbox_fade_out</x:t>
-  </x:si>
-  <x:si>
-    <x:t>── 화면 전체 (screen)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scene_transition</x:t>
-  </x:si>
-  <x:si>
-    <x:t>── 대화창 / UI (ui)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그럼 인수인계를 시작하겠습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bgm_calm_morning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 색조 (분노/상태이상)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이핑 일시 정지 (극적 침묵)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>천천히 배우면 될 거라 생각합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>── 캐릭터 단독 (char)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상점 입장 (동일 유지 시 복사)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: alpha 0↔1, yoyo, repeat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fadeOut → onComplete: 다음 시트 로드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.fadeOut → alpha 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 복합 사용: Happy|Door  처럼 | 로 구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sprite.setTint → clearTint()</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: scaleX/Y→scale, yoyo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>저는 외곽 지부에 이전 관리자 노아(Noa)라고 합니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>말 그대로 외각 지부입니다, 별 볼 일 없는 곳이죠.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.zoomTo(zoom, dur)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>L</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C</x:t>
-  </x:si>
-  <x:si>
-    <x:t>001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>메모</x:t>
-  </x:si>
-  <x:si>
-    <x:t>003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단축어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Y</x:t>
-  </x:si>
-  <x:si>
-    <x:t>설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F</x:t>
-  </x:si>
-  <x:si>
-    <x:t>030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>I</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>R</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>???</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ui</x:t>
-  </x:si>
-  <x:si>
-    <x:t>005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>END</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H</x:t>
-  </x:si>
-  <x:si>
-    <x:t>020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Noa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복합</x:t>
-  </x:si>
-  <x:si>
-    <x:t>D</x:t>
-  </x:si>
-  <x:si>
-    <x:t>노아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G</x:t>
-  </x:si>
-  <x:si>
-    <x:t>N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sad</x:t>
-  </x:si>
-  <x:si>
-    <x:t>all</x:t>
-  </x:si>
-  <x:si>
-    <x:t>009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예약어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q</x:t>
-  </x:si>
-  <x:si>
-    <x:t>010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_cancel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화면 페이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_sad_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sprite.x+=dist; tweens: x-=dist, alpha→1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sprite.x-=dist; tweens: x+=dist, alpha→1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무튼, 새롭게 외각 지부 관리자로 부임하신 것을 축하드립니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.fadeOut(dur, r, g, b)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 별칭을 대사 시트 sfx 컬럼에 입력 — 파일명 자동 매핑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogManager.pauseTyping(duration)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.shake(dur, intensity)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.fadeIn(dur, r, g, b)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: x ±intensity, yoyo, repeat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.flash(dur, r, g, b)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: dialogBox alpha 0.2→1, yoyo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogManager.setTypingSpeed(speed)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogBox.setAlpha(0); tweens: alpha→1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: dialogBox x ±intensity, yoyo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.flash(dur, 255,255,255)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: y-=height, yoyo, ease:Bounce</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGM 파일명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>expr</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UI 취소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SFX 파일명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Happy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 열림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ BG ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>choice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반갑습니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zoom_in</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씬 전환 연출</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배경 파일명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬픈 반응</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shop_In</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상점 해금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>line_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>screen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>target</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카메라 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부임이라니?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Beep</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Shock</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그저 그랬어.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cancel</x:t>
   </x:si>
   <x:si>
-    <x:t>대화창 진동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외곽 지부?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Door</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시스템 알림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이벤트 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ FX ]</x:t>
+    <x:t>Day_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 파라미터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>fade_in</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기쁜 반응</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화창 번쩍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 바운스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>speed=2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UI 확인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>goto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>충격/놀람</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Typing</x:t>
   </x:si>
   <x:si>
     <x:t>타이핑 루프</x:t>
   </x:si>
   <x:si>
+    <x:t>1일차 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Confirm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[ BGM ]</x:t>
+  </x:si>
+  <x:si>
     <x:t>[ SFX ]</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fade_in</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 바운스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카메라 줌 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[ BGM ]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>대화창 번쩍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Day_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Player</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기쁜 반응</x:t>
-  </x:si>
-  <x:si>
-    <x:t>goto</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Confirm</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1일차 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>speed=2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>충격/놀람</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 파라미터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Typing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UI 확인</x:t>
-  </x:si>
-  <x:si>
     <x:t>intensity=5, duration=300</x:t>
   </x:si>
   <x:si>
+    <x:t>duration=300, distance=200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>color=ff4444, duration=200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duration=400, color=000000</x:t>
+  </x:si>
+  <x:si>
     <x:t>color=ffffff, duration=200</x:t>
   </x:si>
   <x:si>
+    <x:t>// 플레이어 고정 — 초상화 없음, 수정 불가</x:t>
+  </x:si>
+  <x:si>
+    <x:t>intensity=3, duration=300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>// 이벤트 시트명과 동일하게 작성 — 자동 매핑</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cameras.main.pan(x, y, dur)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tweens: x+=dist, alpha→0</x:t>
+  </x:si>
+  <x:si>
     <x:t>scale=1.15, duration=200</x:t>
   </x:si>
   <x:si>
-    <x:t>intensity=3, duration=300</x:t>
+    <x:t>tweens: dialogBox alpha→0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>intensity=3, duration=200</x:t>
   </x:si>
   <x:si>
     <x:t>tweens: x-=dist, alpha→0</x:t>
   </x:si>
   <x:si>
-    <x:t>tweens: dialogBox alpha→0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 이벤트 시트명과 동일하게 작성 — 자동 매핑</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=300, distance=200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>intensity=3, duration=200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>// 플레이어 고정 — 초상화 없음, 수정 불가</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=400, color=000000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: x+=dist, alpha→0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>color=ff4444, duration=200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cameras.main.pan(x, y, dur)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_door_open</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그렇군요... 잘 쉬세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카메라 줌 아웃 (원복)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_happy_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: alpha→1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_shock_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이벤트 ID (시트명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별칭 (sfx 컬럼에 입력)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>flash_screen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bgm_shop_theme</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slide_in_right</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=250</x:t>
-  </x:si>
-  <x:si>
-    <x:t>닉네임 (대화창 표시명)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slide_in_left</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_beep_alert</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fade_in_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfx_typing_loop</x:t>
-  </x:si>
-  <x:si>
-    <x:t>speed_up_text</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 왼쪽 슬라이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>textbox_flash</x:t>
-  </x:si>
-  <x:si>
-    <x:t>shake_screen</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 오른쪽 슬라이드 아웃</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오른쪽에서 슬라이드 인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>tweens: alpha→0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slide_out_right</x:t>
-  </x:si>
-  <x:si>
-    <x:t>fade_out_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>── 전체 동시 (all)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 번쩍 (피격/강조)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duration=500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scale_up_char</x:t>
-  </x:si>
-  <x:si>
-    <x:t>textbox_shake</x:t>
-  </x:si>
-  <x:si>
-    <x:t>slide_out_left</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타이핑 속도 감속 (강조)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오늘 하루는 어떠셨나요?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>태그 (bg 컬럼에 입력)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>textbox_fade_in</x:t>
-  </x:si>
-  <x:si>
     <x:t>이런, 아무것도 기억나지 않으신가보네요.</x:t>
   </x:si>
   <x:si>
@@ -786,16 +783,13 @@
     <x:t>//관리자 캐릭터가 이름을 공개하기 이전.</x:t>
   </x:si>
   <x:si>
+    <x:t>zoom=1.0, duration=300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>x=0, y=0, duration=500</x:t>
+  </x:si>
+  <x:si>
     <x:t>zoom=1.2, duration=300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>x=0, y=0, duration=500</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zoom=1.0, duration=300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Background_003</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3511,17 +3505,17 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
       <x:c r="A1" s="135" t="s">
-        <x:v>49</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B1" s="136"/>
       <x:c r="C1" s="137"/>
       <x:c r="D1" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
       <x:c r="A2" s="138" t="s">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="138"/>
       <x:c r="C2" s="138"/>
@@ -3529,7 +3523,7 @@
     </x:row>
     <x:row r="3" spans="1:4" ht="16" customHeight="1">
       <x:c r="A3" s="138" t="s">
-        <x:v>10</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B3" s="138"/>
       <x:c r="C3" s="138"/>
@@ -3537,61 +3531,61 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>179</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D4" s="6" t="s">
-        <x:v>223</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="7" t="s">
-        <x:v>90</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B5" s="8" t="s">
-        <x:v>186</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C5" s="9" t="s">
-        <x:v>205</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="D5" s="9"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="10" t="s">
-        <x:v>96</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B6" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C6" s="12" t="s">
-        <x:v>32</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D6" s="12" t="s">
-        <x:v>116</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="13" t="s">
-        <x:v>113</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B7" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C7" s="11" t="s">
-        <x:v>252</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="D7" s="15" t="s">
-        <x:v>99</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="10" t="s">
-        <x:v>76</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B8" s="11"/>
       <x:c r="C8" s="12"/>
@@ -3599,7 +3593,7 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="13" t="s">
-        <x:v>115</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B9" s="14"/>
       <x:c r="C9" s="15"/>
@@ -3607,7 +3601,7 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="10" t="s">
-        <x:v>105</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B10" s="11"/>
       <x:c r="C10" s="12"/>
@@ -3615,7 +3609,7 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="13" t="s">
-        <x:v>87</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B11" s="14"/>
       <x:c r="C11" s="15"/>
@@ -3623,7 +3617,7 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="10" t="s">
-        <x:v>118</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B12" s="11"/>
       <x:c r="C12" s="12"/>
@@ -3631,7 +3625,7 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="13" t="s">
-        <x:v>107</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B13" s="14"/>
       <x:c r="C13" s="15"/>
@@ -3639,7 +3633,7 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="10" t="s">
-        <x:v>89</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B14" s="11"/>
       <x:c r="C14" s="12"/>
@@ -3647,7 +3641,7 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="13" t="s">
-        <x:v>78</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B15" s="14"/>
       <x:c r="C15" s="15"/>
@@ -3655,7 +3649,7 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="10" t="s">
-        <x:v>98</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B16" s="11"/>
       <x:c r="C16" s="12"/>
@@ -3663,7 +3657,7 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="13" t="s">
-        <x:v>75</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B17" s="14"/>
       <x:c r="C17" s="15"/>
@@ -3671,7 +3665,7 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="10" t="s">
-        <x:v>95</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B18" s="11"/>
       <x:c r="C18" s="12"/>
@@ -3679,7 +3673,7 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="13" t="s">
-        <x:v>119</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B19" s="14"/>
       <x:c r="C19" s="15"/>
@@ -3687,7 +3681,7 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="10" t="s">
-        <x:v>91</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B20" s="11"/>
       <x:c r="C20" s="12"/>
@@ -3695,7 +3689,7 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B21" s="14"/>
       <x:c r="C21" s="15"/>
@@ -3703,7 +3697,7 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="10" t="s">
-        <x:v>124</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B22" s="11"/>
       <x:c r="C22" s="12"/>
@@ -3711,7 +3705,7 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="13" t="s">
-        <x:v>94</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B23" s="14"/>
       <x:c r="C23" s="15"/>
@@ -3719,7 +3713,7 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="10" t="s">
-        <x:v>111</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="12"/>
@@ -3727,7 +3721,7 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="13" t="s">
-        <x:v>92</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B25" s="14"/>
       <x:c r="C25" s="15"/>
@@ -3789,7 +3783,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
       <x:c r="A1" s="135" t="s">
-        <x:v>151</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B1" s="136"/>
       <x:c r="C1" s="137"/>
@@ -3797,7 +3791,7 @@
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
       <x:c r="A2" s="138" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="138"/>
       <x:c r="C2" s="138"/>
@@ -3805,7 +3799,7 @@
     </x:row>
     <x:row r="3" spans="1:4" ht="16" customHeight="1">
       <x:c r="A3" s="138" t="s">
-        <x:v>4</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B3" s="138"/>
       <x:c r="C3" s="138"/>
@@ -3813,49 +3807,45 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="16" t="s">
-        <x:v>248</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>157</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="17" t="s">
-        <x:v>96</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B5" s="18" t="s">
-        <x:v>256</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="19" t="s">
-        <x:v>0</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="20" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B6" s="21" t="s">
-        <x:v>241</x:v>
-      </x:c>
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B6" s="21"/>
       <x:c r="C6" s="22" t="s">
-        <x:v>20</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="17" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="s">
-        <x:v>239</x:v>
-      </x:c>
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B7" s="18"/>
       <x:c r="C7" s="19" t="s">
-        <x:v>17</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
     </x:row>
@@ -3883,7 +3873,7 @@
     <x:mergeCell ref="A2:C2"/>
     <x:mergeCell ref="A3:C3"/>
   </x:mergeCells>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -3903,7 +3893,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
       <x:c r="A1" s="135" t="s">
-        <x:v>183</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B1" s="136"/>
       <x:c r="C1" s="137"/>
@@ -3911,7 +3901,7 @@
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
       <x:c r="A2" s="138" t="s">
-        <x:v>202</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B2" s="138"/>
       <x:c r="C2" s="138"/>
@@ -3919,7 +3909,7 @@
     </x:row>
     <x:row r="3" spans="1:4" ht="16" customHeight="1">
       <x:c r="A3" s="138" t="s">
-        <x:v>6</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B3" s="138"/>
       <x:c r="C3" s="138"/>
@@ -3927,49 +3917,49 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="16" t="s">
-        <x:v>217</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>145</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="17" t="s">
-        <x:v>185</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B5" s="18" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C5" s="19" t="s">
-        <x:v>190</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="20" t="s">
-        <x:v>48</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>220</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="22" t="s">
-        <x:v>160</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="17" t="s">
-        <x:v>159</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B7" s="18" t="s">
-        <x:v>220</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C7" s="19" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
     </x:row>
@@ -4377,7 +4367,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="19.25">
       <x:c r="A1" s="135" t="s">
-        <x:v>178</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B1" s="136"/>
       <x:c r="C1" s="137"/>
@@ -4385,7 +4375,7 @@
     </x:row>
     <x:row r="2" spans="1:4" ht="16" customHeight="1">
       <x:c r="A2" s="138" t="s">
-        <x:v>133</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B2" s="138"/>
       <x:c r="C2" s="138"/>
@@ -4393,7 +4383,7 @@
     </x:row>
     <x:row r="3" spans="1:4" ht="16" customHeight="1">
       <x:c r="A3" s="138" t="s">
-        <x:v>69</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B3" s="138"/>
       <x:c r="C3" s="138"/>
@@ -4401,109 +4391,109 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="25" t="s">
-        <x:v>218</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>148</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="26" t="s">
-        <x:v>149</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B5" s="18" t="s">
-        <x:v>213</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="19" t="s">
-        <x:v>187</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="27" t="s">
-        <x:v>120</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B6" s="21" t="s">
-        <x:v>128</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C6" s="22" t="s">
-        <x:v>158</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="26" t="s">
-        <x:v>168</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B7" s="18" t="s">
-        <x:v>216</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="19" t="s">
-        <x:v>192</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="27" t="s">
-        <x:v>173</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B8" s="21" t="s">
-        <x:v>210</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C8" s="22" t="s">
-        <x:v>150</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="D8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="26" t="s">
-        <x:v>167</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B9" s="18" t="s">
-        <x:v>226</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C9" s="19" t="s">
-        <x:v>174</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="27" t="s">
-        <x:v>194</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B10" s="21" t="s">
-        <x:v>228</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="22" t="s">
-        <x:v>177</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="D10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="26" t="s">
-        <x:v>189</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B11" s="18" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C11" s="19" t="s">
-        <x:v>195</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D11" s="3"/>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="27" t="s">
-        <x:v>170</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B12" s="21" t="s">
-        <x:v>126</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C12" s="22" t="s">
-        <x:v>147</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D12" s="3"/>
     </x:row>
@@ -4914,7 +4904,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="19.25">
       <x:c r="A1" s="135" t="s">
-        <x:v>176</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B1" s="136"/>
       <x:c r="C1" s="136"/>
@@ -4934,7 +4924,7 @@
     </x:row>
     <x:row r="3" spans="1:6" ht="16" customHeight="1">
       <x:c r="A3" s="138" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="138"/>
       <x:c r="C3" s="138"/>
@@ -4944,7 +4934,7 @@
     </x:row>
     <x:row r="4" spans="1:6" ht="16" customHeight="1">
       <x:c r="A4" s="138" t="s">
-        <x:v>8</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B4" s="138"/>
       <x:c r="C4" s="138"/>
@@ -4954,27 +4944,27 @@
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" s="30" t="s">
-        <x:v>123</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B5" s="31" t="s">
-        <x:v>163</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C5" s="16" t="s">
-        <x:v>193</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F5" s="32" t="s">
-        <x:v>114</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6" ht="28" customHeight="1">
       <x:c r="A6" s="139" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B6" s="139"/>
       <x:c r="C6" s="139"/>
@@ -4984,147 +4974,147 @@
     </x:row>
     <x:row r="7" spans="1:6" ht="28" customHeight="1">
       <x:c r="A7" s="33" t="s">
-        <x:v>232</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="34" t="s">
-        <x:v>162</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C7" s="35" t="s">
-        <x:v>199</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="D7" s="36" t="s">
-        <x:v>25</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E7" s="37" t="s">
-        <x:v>135</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F7" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="28" customHeight="1">
       <x:c r="A8" s="39" t="s">
-        <x:v>219</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="40" t="s">
-        <x:v>162</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C8" s="41" t="s">
-        <x:v>197</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D8" s="42" t="s">
-        <x:v>31</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E8" s="43" t="s">
-        <x:v>138</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F8" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="28" customHeight="1">
       <x:c r="A9" s="33" t="s">
-        <x:v>19</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B9" s="34" t="s">
-        <x:v>162</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C9" s="35" t="s">
-        <x:v>206</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D9" s="36" t="s">
-        <x:v>127</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E9" s="37" t="s">
-        <x:v>132</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F9" s="45" t="s">
-        <x:v>119</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="28" customHeight="1">
       <x:c r="A10" s="39" t="s">
-        <x:v>180</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B10" s="40" t="s">
-        <x:v>162</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C10" s="41" t="s">
-        <x:v>206</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D10" s="42" t="s">
-        <x:v>23</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E10" s="43" t="s">
-        <x:v>136</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F10" s="46" t="s">
-        <x:v>119</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="28" customHeight="1">
       <x:c r="A11" s="33" t="s">
-        <x:v>155</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B11" s="34" t="s">
-        <x:v>162</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C11" s="35" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="D11" s="36" t="s">
-        <x:v>182</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="E11" s="37" t="s">
-        <x:v>74</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F11" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="28" customHeight="1">
       <x:c r="A12" s="39" t="s">
-        <x:v>38</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B12" s="40" t="s">
-        <x:v>162</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C12" s="41" t="s">
-        <x:v>255</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D12" s="42" t="s">
-        <x:v>212</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E12" s="43" t="s">
-        <x:v>74</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F12" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="28" customHeight="1">
       <x:c r="A13" s="33" t="s">
-        <x:v>44</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B13" s="34" t="s">
-        <x:v>162</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C13" s="35" t="s">
-        <x:v>254</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="D13" s="36" t="s">
-        <x:v>164</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E13" s="37" t="s">
-        <x:v>209</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="F13" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="28" customHeight="1">
       <x:c r="A14" s="139" t="s">
-        <x:v>64</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B14" s="139"/>
       <x:c r="C14" s="139"/>
@@ -5134,227 +5124,227 @@
     </x:row>
     <x:row r="15" spans="1:6" ht="28" customHeight="1">
       <x:c r="A15" s="33" t="s">
-        <x:v>51</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B15" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C15" s="35" t="s">
-        <x:v>196</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="D15" s="36" t="s">
-        <x:v>26</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E15" s="37" t="s">
-        <x:v>137</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F15" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6" ht="28" customHeight="1">
       <x:c r="A16" s="39" t="s">
-        <x:v>245</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C16" s="41" t="s">
-        <x:v>203</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D16" s="42" t="s">
-        <x:v>230</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="43" t="s">
-        <x:v>200</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F16" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="28" customHeight="1">
       <x:c r="A17" s="33" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B17" s="38" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C17" s="35" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="B17" s="38" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="s">
-        <x:v>203</x:v>
-      </x:c>
       <x:c r="D17" s="36" t="s">
-        <x:v>233</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E17" s="37" t="s">
-        <x:v>207</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="F17" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="28" customHeight="1">
       <x:c r="A18" s="39" t="s">
-        <x:v>225</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B18" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C18" s="41" t="s">
-        <x:v>203</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D18" s="42" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E18" s="43" t="s">
-        <x:v>130</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="28" customHeight="1">
       <x:c r="A19" s="33" t="s">
-        <x:v>221</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B19" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C19" s="35" t="s">
-        <x:v>203</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="D19" s="36" t="s">
-        <x:v>234</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E19" s="37" t="s">
-        <x:v>129</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F19" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6" ht="28" customHeight="1">
       <x:c r="A20" s="39" t="s">
-        <x:v>237</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C20" s="41" t="s">
-        <x:v>215</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D20" s="42" t="s">
-        <x:v>21</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E20" s="43" t="s">
-        <x:v>235</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F20" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6" ht="28" customHeight="1">
       <x:c r="A21" s="33" t="s">
-        <x:v>227</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B21" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C21" s="35" t="s">
-        <x:v>215</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D21" s="36" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E21" s="37" t="s">
-        <x:v>214</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F21" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6" ht="28" customHeight="1">
       <x:c r="A22" s="39" t="s">
-        <x:v>22</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B22" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C22" s="41" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="D22" s="42" t="s">
-        <x:v>181</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E22" s="43" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="F22" s="44" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="F22" s="44" t="s">
-        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6" ht="28" customHeight="1">
       <x:c r="A23" s="33" t="s">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B23" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C23" s="35" t="s">
-        <x:v>52</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D23" s="36" t="s">
-        <x:v>240</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E23" s="37" t="s">
-        <x:v>66</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F23" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6" ht="28" customHeight="1">
       <x:c r="A24" s="39" t="s">
-        <x:v>46</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B24" s="44" t="s">
-        <x:v>152</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C24" s="41" t="s">
-        <x:v>208</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="D24" s="42" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E24" s="43" t="s">
-        <x:v>70</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F24" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6" ht="28" customHeight="1">
       <x:c r="A25" s="33" t="s">
-        <x:v>243</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B25" s="38" t="s">
-        <x:v>152</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C25" s="35" t="s">
-        <x:v>198</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="D25" s="36" t="s">
-        <x:v>13</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E25" s="37" t="s">
-        <x:v>71</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F25" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6" ht="28" customHeight="1">
       <x:c r="A26" s="139" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B26" s="139"/>
       <x:c r="C26" s="139"/>
@@ -5364,147 +5354,147 @@
     </x:row>
     <x:row r="27" spans="1:6" ht="28" customHeight="1">
       <x:c r="A27" s="33" t="s">
-        <x:v>244</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B27" s="47" t="s">
-        <x:v>101</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C27" s="35" t="s">
-        <x:v>204</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D27" s="36" t="s">
-        <x:v>171</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E27" s="37" t="s">
-        <x:v>142</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F27" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6" ht="28" customHeight="1">
       <x:c r="A28" s="39" t="s">
-        <x:v>231</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="48" t="s">
-        <x:v>101</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C28" s="41" t="s">
-        <x:v>224</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D28" s="42" t="s">
-        <x:v>184</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="E28" s="43" t="s">
-        <x:v>139</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F28" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6" ht="28" customHeight="1">
       <x:c r="A29" s="33" t="s">
-        <x:v>249</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B29" s="47" t="s">
-        <x:v>101</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C29" s="35" t="s">
-        <x:v>222</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D29" s="36" t="s">
-        <x:v>50</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E29" s="37" t="s">
-        <x:v>141</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F29" s="45" t="s">
-        <x:v>119</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6" ht="28" customHeight="1">
       <x:c r="A30" s="39" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B30" s="48" t="s">
-        <x:v>101</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C30" s="41" t="s">
-        <x:v>222</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D30" s="42" t="s">
-        <x:v>34</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E30" s="43" t="s">
-        <x:v>201</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="F30" s="46" t="s">
-        <x:v>119</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6" ht="28" customHeight="1">
       <x:c r="A31" s="33" t="s">
-        <x:v>28</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B31" s="47" t="s">
-        <x:v>101</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C31" s="35" t="s">
-        <x:v>242</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D31" s="36" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E31" s="37" t="s">
-        <x:v>134</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F31" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6" ht="28" customHeight="1">
       <x:c r="A32" s="39" t="s">
-        <x:v>229</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B32" s="48" t="s">
-        <x:v>101</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C32" s="41" t="s">
-        <x:v>191</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="D32" s="42" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E32" s="43" t="s">
-        <x:v>140</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F32" s="44" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6" ht="28" customHeight="1">
       <x:c r="A33" s="33" t="s">
-        <x:v>43</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B33" s="47" t="s">
-        <x:v>101</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C33" s="35" t="s">
-        <x:v>30</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D33" s="36" t="s">
-        <x:v>246</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E33" s="37" t="s">
-        <x:v>140</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F33" s="38" t="s">
-        <x:v>83</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6" ht="28" customHeight="1">
       <x:c r="A34" s="139" t="s">
-        <x:v>238</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B34" s="139"/>
       <x:c r="C34" s="139"/>
@@ -5514,62 +5504,62 @@
     </x:row>
     <x:row r="35" spans="1:6" ht="28" customHeight="1">
       <x:c r="A35" s="33" t="s">
-        <x:v>27</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B35" s="49" t="s">
-        <x:v>121</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C35" s="35" t="s">
-        <x:v>242</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D35" s="36" t="s">
-        <x:v>14</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E35" s="37" t="s">
-        <x:v>68</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F35" s="45" t="s">
-        <x:v>119</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6" ht="28" customHeight="1">
       <x:c r="A36" s="39" t="s">
-        <x:v>33</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B36" s="50" t="s">
-        <x:v>121</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C36" s="41" t="s">
-        <x:v>215</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D36" s="42" t="s">
-        <x:v>15</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E36" s="43" t="s">
-        <x:v>143</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F36" s="46" t="s">
-        <x:v>119</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6" ht="28" customHeight="1">
       <x:c r="A37" s="33" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B37" s="49" t="s">
-        <x:v>121</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C37" s="35" t="s">
-        <x:v>206</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="D37" s="36" t="s">
-        <x:v>156</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E37" s="37" t="s">
-        <x:v>67</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F37" s="45" t="s">
-        <x:v>119</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
@@ -6033,7 +6023,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="56" t="s">
-        <x:v>175</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B1" s="127"/>
       <x:c r="C1" s="123"/>
@@ -6042,7 +6032,7 @@
       <x:c r="F1" s="123"/>
       <x:c r="G1" s="124"/>
       <x:c r="H1" s="56" t="s">
-        <x:v>79</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I1" s="128"/>
       <x:c r="J1" s="124"/>
@@ -6050,7 +6040,7 @@
     </x:row>
     <x:row r="2" spans="1:11" ht="16" customHeight="1">
       <x:c r="A2" s="125" t="s">
-        <x:v>11</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B2" s="125"/>
       <x:c r="C2" s="125"/>
@@ -6065,7 +6055,7 @@
     </x:row>
     <x:row r="3" spans="1:11" ht="16" customHeight="1">
       <x:c r="A3" s="125" t="s">
-        <x:v>9</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B3" s="125"/>
       <x:c r="C3" s="125"/>
@@ -6080,7 +6070,7 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="16" customHeight="1">
       <x:c r="A4" s="125" t="s">
-        <x:v>5</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B4" s="125"/>
       <x:c r="C4" s="125"/>
@@ -6095,7 +6085,7 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="126" t="s">
-        <x:v>35</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B5" s="123"/>
       <x:c r="C5" s="123"/>
@@ -6110,51 +6100,51 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="16" t="s">
-        <x:v>161</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="E6" s="57" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="F6" s="57" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G6" s="51" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H6" s="51" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="I6" s="25" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="J6" s="30" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="K6" s="30" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="C6" s="31" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="E6" s="57" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F6" s="57" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G6" s="51" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H6" s="51" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I6" s="25" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="J6" s="30" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="K6" s="30" t="s">
-        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="58" t="s">
-        <x:v>77</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B7" s="59" t="s">
-        <x:v>97</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C7" s="60" t="s">
-        <x:v>77</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D7" s="61" t="s">
-        <x:v>247</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E7" s="62"/>
       <x:c r="F7" s="63"/>
@@ -6166,20 +6156,20 @@
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="67" t="s">
-        <x:v>85</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B8" s="68" t="s">
-        <x:v>90</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C8" s="69"/>
       <x:c r="D8" s="70" t="s">
-        <x:v>169</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="E8" s="71" t="s">
-        <x:v>86</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="F8" s="72" t="s">
-        <x:v>125</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G8" s="73"/>
       <x:c r="H8" s="73"/>
@@ -6189,20 +6179,20 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="58" t="s">
-        <x:v>80</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B9" s="59" t="s">
-        <x:v>90</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C9" s="76"/>
       <x:c r="D9" s="61" t="s">
-        <x:v>36</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E9" s="77" t="s">
-        <x:v>86</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="F9" s="78" t="s">
-        <x:v>108</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G9" s="64"/>
       <x:c r="H9" s="64"/>
@@ -6212,80 +6202,80 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="67" t="s">
-        <x:v>125</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B10" s="68" t="s">
-        <x:v>97</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C10" s="79" t="s">
-        <x:v>85</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D10" s="70" t="s">
-        <x:v>211</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E10" s="80"/>
       <x:c r="F10" s="72" t="s">
-        <x:v>88</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G10" s="73"/>
       <x:c r="H10" s="73"/>
       <x:c r="I10" s="81" t="s">
-        <x:v>120</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="J10" s="75"/>
       <x:c r="K10" s="75"/>
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="58" t="s">
-        <x:v>108</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B11" s="59" t="s">
-        <x:v>97</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C11" s="60" t="s">
-        <x:v>80</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D11" s="61" t="s">
-        <x:v>40</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E11" s="62"/>
       <x:c r="F11" s="78" t="s">
-        <x:v>88</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G11" s="82" t="s">
-        <x:v>41</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H11" s="64"/>
       <x:c r="I11" s="65"/>
       <x:c r="J11" s="83" t="s">
-        <x:v>51</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K11" s="66"/>
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="67" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B12" s="68" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="C12" s="79" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D12" s="70" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="B12" s="68" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="C12" s="79" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D12" s="70" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="E12" s="80"/>
       <x:c r="F12" s="72" t="s">
-        <x:v>104</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G12" s="84" t="s">
-        <x:v>47</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H12" s="73"/>
       <x:c r="I12" s="74"/>
       <x:c r="J12" s="85" t="s">
-        <x:v>19</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K12" s="75"/>
     </x:row>
@@ -7694,7 +7684,7 @@
       <x:c r="K120" s="3"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -7720,7 +7710,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="96" t="s">
-        <x:v>175</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B1" s="133"/>
       <x:c r="C1" s="130"/>
@@ -7729,7 +7719,7 @@
       <x:c r="F1" s="130"/>
       <x:c r="G1" s="131"/>
       <x:c r="H1" s="96" t="s">
-        <x:v>79</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I1" s="134"/>
       <x:c r="J1" s="131"/>
@@ -7737,7 +7727,7 @@
     </x:row>
     <x:row r="2" spans="1:11" ht="16" customHeight="1">
       <x:c r="A2" s="132" t="s">
-        <x:v>11</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B2" s="132"/>
       <x:c r="C2" s="132"/>
@@ -7752,7 +7742,7 @@
     </x:row>
     <x:row r="3" spans="1:11" ht="16" customHeight="1">
       <x:c r="A3" s="132" t="s">
-        <x:v>9</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B3" s="132"/>
       <x:c r="C3" s="132"/>
@@ -7767,7 +7757,7 @@
     </x:row>
     <x:row r="4" spans="1:11" ht="16" customHeight="1">
       <x:c r="A4" s="132" t="s">
-        <x:v>5</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B4" s="132"/>
       <x:c r="C4" s="132"/>
@@ -7782,7 +7772,7 @@
     </x:row>
     <x:row r="5" spans="1:11">
       <x:c r="A5" s="129" t="s">
-        <x:v>35</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B5" s="130"/>
       <x:c r="C5" s="130"/>
@@ -7797,51 +7787,51 @@
     </x:row>
     <x:row r="6" spans="1:11">
       <x:c r="A6" s="97" t="s">
-        <x:v>161</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B6" s="98" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C6" s="99" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D6" s="100" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="E6" s="101" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="F6" s="101" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G6" s="102" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H6" s="102" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="I6" s="103" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="J6" s="104" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="K6" s="104" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="C6" s="99" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D6" s="100" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="E6" s="101" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="F6" s="101" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="G6" s="102" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="H6" s="102" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I6" s="103" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="J6" s="104" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="K6" s="104" t="s">
-        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:11">
       <x:c r="A7" s="105" t="s">
-        <x:v>77</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B7" s="106" t="s">
-        <x:v>113</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C7" s="107" t="s">
-        <x:v>77</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D7" s="108" t="s">
-        <x:v>154</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E7" s="114"/>
       <x:c r="F7" s="115"/>
@@ -7850,21 +7840,21 @@
       <x:c r="I7" s="122"/>
       <x:c r="J7" s="7"/>
       <x:c r="K7" s="119" t="s">
-        <x:v>96</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:11">
       <x:c r="A8" s="109" t="s">
-        <x:v>85</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B8" s="110" t="s">
-        <x:v>96</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C8" s="116" t="s">
-        <x:v>77</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D8" s="111" t="s">
-        <x:v>72</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E8" s="112"/>
       <x:c r="F8" s="113"/>
@@ -7876,20 +7866,20 @@
     </x:row>
     <x:row r="9" spans="1:11">
       <x:c r="A9" s="105" t="s">
-        <x:v>80</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B9" s="106" t="s">
-        <x:v>90</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C9" s="107"/>
       <x:c r="D9" s="108" t="s">
-        <x:v>172</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="E9" s="114" t="s">
-        <x:v>86</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="F9" s="115" t="s">
-        <x:v>112</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="G9" s="118"/>
       <x:c r="H9" s="118"/>
@@ -7899,16 +7889,16 @@
     </x:row>
     <x:row r="10" spans="1:11">
       <x:c r="A10" s="109" t="s">
-        <x:v>112</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B10" s="110" t="s">
-        <x:v>96</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C10" s="116" t="s">
-        <x:v>80</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D10" s="111" t="s">
-        <x:v>73</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E10" s="112"/>
       <x:c r="F10" s="113"/>
@@ -7920,16 +7910,16 @@
     </x:row>
     <x:row r="11" spans="1:11">
       <x:c r="A11" s="105" t="s">
-        <x:v>102</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B11" s="106" t="s">
-        <x:v>96</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C11" s="107" t="s">
-        <x:v>77</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D11" s="108" t="s">
-        <x:v>131</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E11" s="114"/>
       <x:c r="F11" s="115"/>
@@ -7941,20 +7931,20 @@
     </x:row>
     <x:row r="12" spans="1:11">
       <x:c r="A12" s="109" t="s">
-        <x:v>117</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B12" s="110" t="s">
-        <x:v>90</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C12" s="116"/>
       <x:c r="D12" s="111" t="s">
-        <x:v>166</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E12" s="112" t="s">
-        <x:v>86</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="F12" s="113" t="s">
-        <x:v>109</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="G12" s="120"/>
       <x:c r="H12" s="120"/>
@@ -7964,16 +7954,16 @@
     </x:row>
     <x:row r="13" spans="1:11" ht="18" customHeight="1">
       <x:c r="A13" s="17" t="s">
-        <x:v>109</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B13" s="86" t="s">
-        <x:v>96</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C13" s="87" t="s">
-        <x:v>80</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D13" s="88" t="s">
-        <x:v>250</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E13" s="89"/>
       <x:c r="F13" s="90"/>
@@ -7985,16 +7975,16 @@
     </x:row>
     <x:row r="14" spans="1:11" ht="18" customHeight="1">
       <x:c r="A14" s="20" t="s">
-        <x:v>103</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B14" s="91" t="s">
-        <x:v>96</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C14" s="92" t="s">
-        <x:v>85</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D14" s="93" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E14" s="94"/>
       <x:c r="F14" s="95"/>
@@ -8006,16 +7996,16 @@
     </x:row>
     <x:row r="15" spans="1:11" ht="18" customHeight="1">
       <x:c r="A15" s="17" t="s">
-        <x:v>122</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B15" s="86" t="s">
-        <x:v>96</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C15" s="87" t="s">
-        <x:v>77</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D15" s="88" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E15" s="89"/>
       <x:c r="F15" s="90"/>
@@ -8027,16 +8017,16 @@
     </x:row>
     <x:row r="16" spans="1:11" ht="18" customHeight="1">
       <x:c r="A16" s="20" t="s">
-        <x:v>125</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B16" s="91" t="s">
-        <x:v>96</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C16" s="92" t="s">
-        <x:v>80</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D16" s="93" t="s">
-        <x:v>59</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E16" s="94"/>
       <x:c r="F16" s="95"/>
@@ -9399,7 +9389,7 @@
       <x:c r="K120" s="3"/>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51166665554046631" footer="0.51166665554046631"/>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51138889789581299" footer="0.51138889789581299"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>